--- a/IR_Organiza.xlsx
+++ b/IR_Organiza.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Aulas Santander\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Pictures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{225CDA65-B07A-4744-AC5C-5C738E48E432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5425FD1-FA53-4364-9A01-1938684D36F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="0" xr2:uid="{57163484-8E5B-4030-BED2-518B128ABEF5}"/>
   </bookViews>
@@ -32,7 +32,6 @@
     <definedName name="ListaRendimentos">TABELA!$E$8:$E$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1109,16 +1108,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyProtection="1">
       <protection hidden="1"/>
@@ -1141,14 +1132,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
@@ -1260,10 +1243,6 @@
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
@@ -1352,12 +1331,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection hidden="1"/>
@@ -1366,30 +1339,26 @@
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="168" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="168" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -1419,12 +1388,6 @@
     <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
@@ -1443,14 +1406,33 @@
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="168" fontId="23" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="19" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -1698,42 +1680,36 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color theme="1"/>
-        <name val="Aptos Display"/>
+        <name val="Segoe UI"/>
         <family val="2"/>
-        <scheme val="major"/>
+        <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="1" hidden="1"/>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color theme="1"/>
-        <name val="Aptos Narrow"/>
+        <name val="Segoe UI"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="1" hidden="1"/>
     </dxf>
     <dxf>
@@ -1836,6 +1812,26 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="1"/>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1848,7 +1844,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="1" hidden="1"/>
     </dxf>
     <dxf>
@@ -1968,18 +1964,21 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color theme="1"/>
-        <name val="Segoe UI"/>
+        <name val="Aptos Display"/>
         <family val="2"/>
-        <scheme val="none"/>
+        <scheme val="major"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="1" hidden="1"/>
     </dxf>
@@ -2253,23 +2252,6 @@
         <family val="2"/>
         <scheme val="major"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="1" hidden="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="1" hidden="1"/>
     </dxf>
@@ -4217,7 +4199,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -10864,6 +10845,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>R$ 27.006,30</a:t>
           </a:fld>
           <a:endParaRPr lang="pt-BR" sz="1800" b="1" i="0">
@@ -10939,6 +10921,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>3</a:t>
           </a:fld>
           <a:endParaRPr lang="pt-BR" sz="1800" b="1" i="0">
@@ -11014,6 +10997,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>8</a:t>
           </a:fld>
           <a:endParaRPr lang="pt-BR" sz="1800" b="1" i="0">
@@ -11089,6 +11073,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>2</a:t>
           </a:fld>
           <a:endParaRPr lang="pt-BR" sz="1800" b="1" i="0">
@@ -13275,7 +13260,7 @@
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="15" name="Retângulo: Cantos Arredondados 14">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB7EFCC1-3D5C-4A17-895E-0544EE239552}"/>
@@ -21927,6 +21912,7 @@
                 </a:solidFill>
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
+              <a:pPr algn="ctr"/>
               <a:t>33%</a:t>
             </a:fld>
             <a:endParaRPr lang="pt-BR" sz="1200" b="1">
@@ -22355,6 +22341,7 @@
                 </a:solidFill>
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
+              <a:pPr algn="ctr"/>
               <a:t>90%</a:t>
             </a:fld>
             <a:endParaRPr lang="pt-BR" sz="1200" b="1">
@@ -22416,6 +22403,7 @@
                 </a:solidFill>
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
+              <a:pPr algn="ctr"/>
               <a:t>100%</a:t>
             </a:fld>
             <a:endParaRPr lang="pt-BR" sz="1200" b="1">
@@ -22477,6 +22465,7 @@
                 </a:solidFill>
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
+              <a:pPr algn="ctr"/>
               <a:t>80%</a:t>
             </a:fld>
             <a:endParaRPr lang="pt-BR" sz="1200" b="1">
@@ -22538,6 +22527,7 @@
                 </a:solidFill>
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
+              <a:pPr algn="ctr"/>
               <a:t>80%</a:t>
             </a:fld>
             <a:endParaRPr lang="pt-BR" sz="1200" b="1">
@@ -23352,16 +23342,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{ED3D514B-62F1-4DF0-AF57-2E36C4F1B5EF}" name="Tabela13" displayName="Tabela13" ref="C13:I51" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{ED3D514B-62F1-4DF0-AF57-2E36C4F1B5EF}" name="Tabela13" displayName="Tabela13" ref="C13:I51" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
   <autoFilter ref="C13:I51" xr:uid="{ED3D514B-62F1-4DF0-AF57-2E36C4F1B5EF}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{940EA324-F0E5-4F1D-82BB-A099E28B4318}" name="DATA" dataDxfId="52"/>
-    <tableColumn id="2" xr3:uid="{4630F158-C596-47EF-9C6D-4075206D8689}" name="FONTE PAGADORA" dataDxfId="51"/>
-    <tableColumn id="3" xr3:uid="{22A382ED-D94E-4D27-A773-4B7A944A4592}" name="CPF/CNPJ" dataDxfId="50"/>
-    <tableColumn id="4" xr3:uid="{93254152-B993-4E3E-9B74-E0EFB8717546}" name="TIPO DE RENDIMENTO" dataDxfId="49"/>
-    <tableColumn id="5" xr3:uid="{82B15570-66F5-40FE-9546-8C957E677F94}" name="VALOR RECEBIDO" dataDxfId="48"/>
-    <tableColumn id="7" xr3:uid="{734A33EB-B294-48D4-A04B-61E98842A4A9}" name="IMPOSTO RETIDO" dataDxfId="47" dataCellStyle="Moeda"/>
-    <tableColumn id="9" xr3:uid="{5200F33D-650F-4601-B83A-283F57F3572D}" name="SITUAÇÃO" dataDxfId="55">
+    <tableColumn id="1" xr3:uid="{940EA324-F0E5-4F1D-82BB-A099E28B4318}" name="DATA" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{4630F158-C596-47EF-9C6D-4075206D8689}" name="FONTE PAGADORA" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{22A382ED-D94E-4D27-A773-4B7A944A4592}" name="CPF/CNPJ" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{93254152-B993-4E3E-9B74-E0EFB8717546}" name="TIPO DE RENDIMENTO" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{82B15570-66F5-40FE-9546-8C957E677F94}" name="VALOR RECEBIDO" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{734A33EB-B294-48D4-A04B-61E98842A4A9}" name="IMPOSTO RETIDO" dataDxfId="48" dataCellStyle="Moeda"/>
+    <tableColumn id="9" xr3:uid="{5200F33D-650F-4601-B83A-283F57F3572D}" name="SITUAÇÃO" dataDxfId="47">
       <calculatedColumnFormula>IF(COUNTA(C14:H14)=0,"",IF(OR(C14="",D14="",E14="",F14="",G14="",#REF!="",#REF!=""),"INCOMPLETO",IF(#REF!="SIM","CONCLUÍDO","PENDENTE")))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -23370,16 +23360,16 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{27FABA0B-5301-4C06-81A3-676B369D108E}" name="Tabela138" displayName="Tabela138" ref="C13:I51" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{27FABA0B-5301-4C06-81A3-676B369D108E}" name="Tabela138" displayName="Tabela138" ref="C13:I51" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
   <autoFilter ref="C13:I51" xr:uid="{ED3D514B-62F1-4DF0-AF57-2E36C4F1B5EF}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{B8089B97-9BDE-408A-9B49-B19DCA8F4BFB}" name="DATA" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{7EE7C9B0-CBC9-49F0-B2E7-BFE84497B23C}" name="PRESTADOR / RECEBEDOR" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{FE3F45CE-A2AE-488A-AAB9-3A34E0D10F02}" name="CPF/CNPJ" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{3B3CBBB2-EBEB-4288-8564-66A47AE0696D}" name="TIPO DE DESPESA" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{61438414-4DEE-434F-AD4A-CE81B3B848CF}" name="VALOR PAGO" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{39246360-47AE-4386-8BAF-2E82B23B7F63}" name="VALOR REEMBOLSADO" dataDxfId="38" dataCellStyle="Moeda"/>
-    <tableColumn id="9" xr3:uid="{10E529A4-1CF6-43A8-8B2D-D76465F47446}" name="SITUAÇÃO" dataDxfId="46">
+    <tableColumn id="1" xr3:uid="{B8089B97-9BDE-408A-9B49-B19DCA8F4BFB}" name="DATA" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{7EE7C9B0-CBC9-49F0-B2E7-BFE84497B23C}" name="PRESTADOR / RECEBEDOR" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{FE3F45CE-A2AE-488A-AAB9-3A34E0D10F02}" name="CPF/CNPJ" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{3B3CBBB2-EBEB-4288-8564-66A47AE0696D}" name="TIPO DE DESPESA" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{61438414-4DEE-434F-AD4A-CE81B3B848CF}" name="VALOR PAGO" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{39246360-47AE-4386-8BAF-2E82B23B7F63}" name="VALOR REEMBOLSADO" dataDxfId="39" dataCellStyle="Moeda"/>
+    <tableColumn id="9" xr3:uid="{10E529A4-1CF6-43A8-8B2D-D76465F47446}" name="SITUAÇÃO" dataDxfId="21">
       <calculatedColumnFormula>IF(COUNTA(C14:H14)=0,"",IF(OR(C14="",D14="",E14="",F14="",G14="",#REF!="",#REF!=""),"INCOMPLETO",IF(#REF!="SIM","CONCLUÍDO","PENDENTE")))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -23388,16 +23378,16 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{750FA862-BEBF-43EB-A624-2B2F34B689C0}" name="Tabela139" displayName="Tabela139" ref="C13:I51" totalsRowShown="0" headerRowDxfId="21" dataDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{750FA862-BEBF-43EB-A624-2B2F34B689C0}" name="Tabela139" displayName="Tabela139" ref="C13:I51" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
   <autoFilter ref="C13:I51" xr:uid="{ED3D514B-62F1-4DF0-AF57-2E36C4F1B5EF}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{37115DF0-FE33-4379-994C-64ED66CE2B77}" name="TIPO DE BEM" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{3DC07E1E-7443-4ACE-B9FD-C0A41341143E}" name="DESCRIÇÃO" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{B56CB006-894B-4B19-A63A-18501FA2D9D5}" name="LOCALIZAÇÃO" dataDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{D526C6D8-0BB7-472C-B700-5B730C5FAC23}" name="DATA DE AQUISIÇÃO" dataDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{B9C0CFE1-3B93-4A90-BD34-38FC5F496B84}" name="VALOR ANTERIOR" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{8305B14C-BE03-4BB7-8299-609566E9B8B1}" name="VALOR ATUAL" dataDxfId="30" dataCellStyle="Moeda"/>
-    <tableColumn id="9" xr3:uid="{F7547426-64B3-4497-816A-24009459ADB8}" name="SITUAÇÃO" dataDxfId="37">
+    <tableColumn id="1" xr3:uid="{37115DF0-FE33-4379-994C-64ED66CE2B77}" name="TIPO DE BEM" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{3DC07E1E-7443-4ACE-B9FD-C0A41341143E}" name="DESCRIÇÃO" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{B56CB006-894B-4B19-A63A-18501FA2D9D5}" name="LOCALIZAÇÃO" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{D526C6D8-0BB7-472C-B700-5B730C5FAC23}" name="DATA DE AQUISIÇÃO" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{B9C0CFE1-3B93-4A90-BD34-38FC5F496B84}" name="VALOR ANTERIOR" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{8305B14C-BE03-4BB7-8299-609566E9B8B1}" name="VALOR ATUAL" dataDxfId="31" dataCellStyle="Moeda"/>
+    <tableColumn id="9" xr3:uid="{F7547426-64B3-4497-816A-24009459ADB8}" name="SITUAÇÃO" dataDxfId="30">
       <calculatedColumnFormula>IF(COUNTA(C14:H14)=0,"",IF(OR(C14="",D14="",E14="",F14="",G14="",H14=""),"INCOMPLETO","CONCLUÍDO"))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -23406,7 +23396,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{ABA599E1-9663-4DC6-AC52-308B7D58F2C8}" name="Tabela13910" displayName="Tabela13910" ref="C13:H51" totalsRowShown="0" headerRowDxfId="22" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{ABA599E1-9663-4DC6-AC52-308B7D58F2C8}" name="Tabela13910" displayName="Tabela13910" ref="C13:H51" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
   <autoFilter ref="C13:H51" xr:uid="{ED3D514B-62F1-4DF0-AF57-2E36C4F1B5EF}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{01A085CC-6DA1-4047-95D6-9AD6006965B4}" name="DOCUMENTO" dataDxfId="27"/>
@@ -23414,7 +23404,7 @@
     <tableColumn id="3" xr3:uid="{DBD1B425-5158-4B9C-8388-5262D874FCA7}" name="ANO-CALENDÁRIO" dataDxfId="25"/>
     <tableColumn id="4" xr3:uid="{F119BBCE-1207-4FAC-9615-87D505404C3B}" name="RECEBIDO?" dataDxfId="24"/>
     <tableColumn id="5" xr3:uid="{B68D6540-2B3E-405C-86BD-D86320A85B6A}" name="LOCAL DO ARQUIVO" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{B5F8778C-ECF6-46A6-8E96-AC0B25AECC2A}" name="SITUAÇÃO" dataDxfId="29" dataCellStyle="Moeda">
+    <tableColumn id="7" xr3:uid="{B5F8778C-ECF6-46A6-8E96-AC0B25AECC2A}" name="SITUAÇÃO" dataDxfId="22" dataCellStyle="Moeda">
       <calculatedColumnFormula>IF(COUNTA(C14:G14)=0,"",IF(OR(C14="",D14="",E14="",F14=""),"INCOMPLETO",IF(F14="NÃO","PENDENTE",IF(G14="","INCOMPLETO","CONCLUÍDO"))))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -23745,533 +23735,533 @@
   <dimension ref="A1:Q60"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.54296875" style="5" customWidth="1"/>
-    <col min="2" max="11" width="12.6328125" style="35" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" style="5" customWidth="1"/>
-    <col min="13" max="13" width="8.7265625" style="5" customWidth="1"/>
-    <col min="14" max="16384" width="8.7265625" style="5" hidden="1"/>
+    <col min="1" max="1" width="3.54296875" style="3" customWidth="1"/>
+    <col min="2" max="11" width="12.6328125" style="31" customWidth="1"/>
+    <col min="12" max="12" width="12.6328125" style="3" customWidth="1"/>
+    <col min="13" max="13" width="8.7265625" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="8.7265625" style="3" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="10" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-    </row>
-    <row r="12" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-    </row>
-    <row r="13" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-    </row>
-    <row r="14" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="2:8" s="5" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B16" s="13"/>
+    <row r="1" spans="2:8" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:8" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:8" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:8" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="2:8" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="2:8" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="2:8" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="2:8" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="2:8" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="2:8" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="2:8" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="86"/>
+      <c r="C11" s="86"/>
+      <c r="D11" s="86"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="86"/>
+      <c r="H11" s="86"/>
+    </row>
+    <row r="12" spans="2:8" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="87"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="87"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="87"/>
+      <c r="H12" s="87"/>
+    </row>
+    <row r="13" spans="2:8" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="87"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="87"/>
+      <c r="F13" s="87"/>
+      <c r="G13" s="87"/>
+      <c r="H13" s="87"/>
+    </row>
+    <row r="14" spans="2:8" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="2:8" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="2:8" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B16" s="9"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="N25" s="14">
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="N25" s="10">
         <v>0</v>
       </c>
-      <c r="P25" s="15" t="s">
+      <c r="P25" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="Q25" s="16" t="s">
+      <c r="Q25" s="12" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="26" spans="2:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="P26" s="17">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="P26" s="13">
         <f>IFERROR(COUNTIF(DOCUMENTOS!F14:F51,"SIM")/COUNTA(DOCUMENTOS!C14:C51),0)</f>
         <v>0.8</v>
       </c>
-      <c r="Q26" s="14">
+      <c r="Q26" s="10">
         <f>1-P26</f>
         <v>0.19999999999999996</v>
       </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.35"/>
     <row r="44" spans="2:11" x14ac:dyDescent="0.35"/>
     <row r="45" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B45" s="81">
+      <c r="B45" s="73">
         <f>SUM(RENDIMENTOS!G:G)</f>
         <v>27006.3</v>
       </c>
-      <c r="C45" s="40"/>
-      <c r="E45" s="82"/>
-      <c r="F45" s="86" t="s">
+      <c r="C45" s="36"/>
+      <c r="E45" s="74"/>
+      <c r="F45" s="88" t="s">
         <v>243</v>
       </c>
-      <c r="G45" s="86"/>
-      <c r="H45" s="86"/>
+      <c r="G45" s="88"/>
+      <c r="H45" s="88"/>
     </row>
     <row r="46" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="40">
+      <c r="B46" s="36">
         <f>COUNTA(BANCOS!D13,BANCOS!D26,BANCOS!D39)</f>
         <v>3</v>
       </c>
-      <c r="C46" s="40"/>
-      <c r="E46" s="82"/>
-      <c r="F46" s="85" t="s">
+      <c r="C46" s="36"/>
+      <c r="E46" s="74"/>
+      <c r="F46" s="77" t="s">
         <v>244</v>
       </c>
-      <c r="G46" s="84" t="s">
+      <c r="G46" s="76" t="s">
         <v>245</v>
       </c>
-      <c r="H46" s="83" t="s">
+      <c r="H46" s="75" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="47" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="40">
+      <c r="B47" s="36">
         <f>COUNTIF(DOCUMENTOS!F14:F51,"SIM")</f>
         <v>8</v>
       </c>
-      <c r="C47" s="40"/>
-      <c r="E47" s="82"/>
-      <c r="F47" s="87" t="s">
+      <c r="C47" s="36"/>
+      <c r="E47" s="74"/>
+      <c r="F47" s="85" t="s">
         <v>246</v>
       </c>
-      <c r="G47" s="87"/>
-      <c r="H47" s="87"/>
+      <c r="G47" s="85"/>
+      <c r="H47" s="85"/>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B48" s="40">
+      <c r="B48" s="36">
         <f>COUNTIF(DOCUMENTOS!H14:H51,"PENDENTE")+COUNTIF(DOCUMENTOS!H14:H51,"INCOMPLETO")</f>
         <v>2</v>
       </c>
-      <c r="C48" s="40"/>
-      <c r="E48" s="82"/>
+      <c r="C48" s="36"/>
+      <c r="E48" s="74"/>
     </row>
     <row r="49" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="E49" s="82"/>
-      <c r="G49" s="82"/>
-      <c r="H49" s="82"/>
+      <c r="E49" s="74"/>
+      <c r="G49" s="74"/>
+      <c r="H49" s="74"/>
     </row>
     <row r="50" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="E50" s="82"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="82"/>
-      <c r="H50" s="82"/>
+      <c r="E50" s="74"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="74"/>
+      <c r="H50" s="74"/>
     </row>
     <row r="51" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="E51" s="82"/>
-      <c r="G51" s="82"/>
-      <c r="H51" s="82"/>
-      <c r="I51" s="82"/>
-      <c r="J51" s="82"/>
-      <c r="K51" s="82"/>
+      <c r="E51" s="74"/>
+      <c r="G51" s="74"/>
+      <c r="H51" s="74"/>
+      <c r="I51" s="74"/>
+      <c r="J51" s="74"/>
+      <c r="K51" s="74"/>
     </row>
     <row r="52" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="E52" s="82"/>
-      <c r="F52" s="82"/>
-      <c r="G52" s="82"/>
-      <c r="H52" s="82"/>
-      <c r="I52" s="82"/>
-      <c r="J52" s="82"/>
-      <c r="K52" s="82"/>
+      <c r="E52" s="74"/>
+      <c r="F52" s="74"/>
+      <c r="G52" s="74"/>
+      <c r="H52" s="74"/>
+      <c r="I52" s="74"/>
+      <c r="J52" s="74"/>
+      <c r="K52" s="74"/>
     </row>
     <row r="53" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="E53" s="82"/>
-      <c r="F53" s="82"/>
-      <c r="G53" s="82"/>
-      <c r="H53" s="82"/>
-      <c r="I53" s="82"/>
-      <c r="J53" s="82"/>
-      <c r="K53" s="82"/>
+      <c r="E53" s="74"/>
+      <c r="F53" s="74"/>
+      <c r="G53" s="74"/>
+      <c r="H53" s="74"/>
+      <c r="I53" s="74"/>
+      <c r="J53" s="74"/>
+      <c r="K53" s="74"/>
     </row>
     <row r="54" spans="5:11" x14ac:dyDescent="0.35">
-      <c r="E54" s="82"/>
-      <c r="F54" s="82"/>
-      <c r="G54" s="82"/>
-      <c r="H54" s="82"/>
-      <c r="I54" s="82"/>
-      <c r="J54" s="82"/>
-      <c r="K54" s="82"/>
+      <c r="E54" s="74"/>
+      <c r="F54" s="74"/>
+      <c r="G54" s="74"/>
+      <c r="H54" s="74"/>
+      <c r="I54" s="74"/>
+      <c r="J54" s="74"/>
+      <c r="K54" s="74"/>
     </row>
     <row r="55" spans="5:11" hidden="1" x14ac:dyDescent="0.35">
-      <c r="E55" s="82"/>
-      <c r="F55" s="82"/>
-      <c r="G55" s="82"/>
-      <c r="H55" s="82"/>
-      <c r="I55" s="82"/>
-      <c r="J55" s="82"/>
-      <c r="K55" s="82"/>
+      <c r="E55" s="74"/>
+      <c r="F55" s="74"/>
+      <c r="G55" s="74"/>
+      <c r="H55" s="74"/>
+      <c r="I55" s="74"/>
+      <c r="J55" s="74"/>
+      <c r="K55" s="74"/>
     </row>
     <row r="56" spans="5:11" hidden="1" x14ac:dyDescent="0.35">
-      <c r="E56" s="82"/>
-      <c r="F56" s="82"/>
-      <c r="G56" s="82"/>
-      <c r="H56" s="82"/>
-      <c r="I56" s="82"/>
-      <c r="J56" s="82"/>
-      <c r="K56" s="82"/>
+      <c r="E56" s="74"/>
+      <c r="F56" s="74"/>
+      <c r="G56" s="74"/>
+      <c r="H56" s="74"/>
+      <c r="I56" s="74"/>
+      <c r="J56" s="74"/>
+      <c r="K56" s="74"/>
     </row>
     <row r="57" spans="5:11" hidden="1" x14ac:dyDescent="0.35">
-      <c r="E57" s="82"/>
-      <c r="F57" s="82"/>
-      <c r="G57" s="82"/>
-      <c r="H57" s="82"/>
-      <c r="I57" s="82"/>
-      <c r="J57" s="82"/>
-      <c r="K57" s="82"/>
+      <c r="E57" s="74"/>
+      <c r="F57" s="74"/>
+      <c r="G57" s="74"/>
+      <c r="H57" s="74"/>
+      <c r="I57" s="74"/>
+      <c r="J57" s="74"/>
+      <c r="K57" s="74"/>
     </row>
     <row r="58" spans="5:11" hidden="1" x14ac:dyDescent="0.35">
-      <c r="E58" s="82"/>
-      <c r="F58" s="82"/>
-      <c r="G58" s="82"/>
-      <c r="H58" s="82"/>
-      <c r="I58" s="82"/>
-      <c r="J58" s="82"/>
-      <c r="K58" s="82"/>
+      <c r="E58" s="74"/>
+      <c r="F58" s="74"/>
+      <c r="G58" s="74"/>
+      <c r="H58" s="74"/>
+      <c r="I58" s="74"/>
+      <c r="J58" s="74"/>
+      <c r="K58" s="74"/>
     </row>
     <row r="59" spans="5:11" hidden="1" x14ac:dyDescent="0.35">
-      <c r="E59" s="82"/>
-      <c r="F59" s="82"/>
-      <c r="G59" s="82"/>
-      <c r="H59" s="82"/>
-      <c r="I59" s="82"/>
-      <c r="J59" s="82"/>
-      <c r="K59" s="82"/>
+      <c r="E59" s="74"/>
+      <c r="F59" s="74"/>
+      <c r="G59" s="74"/>
+      <c r="H59" s="74"/>
+      <c r="I59" s="74"/>
+      <c r="J59" s="74"/>
+      <c r="K59" s="74"/>
     </row>
     <row r="60" spans="5:11" hidden="1" x14ac:dyDescent="0.35">
-      <c r="E60" s="82"/>
-      <c r="F60" s="82"/>
-      <c r="G60" s="82"/>
-      <c r="H60" s="82"/>
-      <c r="I60" s="82"/>
-      <c r="J60" s="82"/>
-      <c r="K60" s="82"/>
+      <c r="E60" s="74"/>
+      <c r="F60" s="74"/>
+      <c r="G60" s="74"/>
+      <c r="H60" s="74"/>
+      <c r="I60" s="74"/>
+      <c r="J60" s="74"/>
+      <c r="K60" s="74"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
@@ -24331,324 +24321,293 @@
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.90625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="42.26953125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="43.26953125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="1.90625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="14.81640625" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="8.7265625" style="5" hidden="1"/>
+    <col min="1" max="1" width="29.90625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.7265625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="42.26953125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="43.26953125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="1.90625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="8.7265625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.81640625" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="3" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:5" x14ac:dyDescent="0.35"/>
     <row r="2" spans="3:5" x14ac:dyDescent="0.35"/>
     <row r="3" spans="3:5" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="34" t="s">
         <v>241</v>
       </c>
-      <c r="D4" s="38"/>
+      <c r="D4" s="34"/>
     </row>
     <row r="5" spans="3:5" x14ac:dyDescent="0.35"/>
     <row r="6" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="18" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="7" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="19">
         <v>12312312398</v>
       </c>
     </row>
     <row r="8" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="20">
         <v>34605</v>
       </c>
     </row>
     <row r="9" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="21">
         <v>31713388</v>
       </c>
     </row>
     <row r="10" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="21" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="11" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="21" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="12" spans="3:5" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="E12" s="21"/>
+      <c r="E12" s="17"/>
     </row>
     <row r="13" spans="3:5" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="D13" s="6"/>
+      <c r="D13" s="4"/>
     </row>
     <row r="14" spans="3:5" x14ac:dyDescent="0.35"/>
     <row r="15" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="21" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="16" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="22">
         <v>245</v>
       </c>
     </row>
-    <row r="17" spans="3:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C17" s="18" t="s">
+    <row r="17" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C17" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="23" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="3:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C18" s="18" t="s">
+    <row r="18" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C18" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="23" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="3:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C19" s="18" t="s">
+    <row r="19" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C19" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
-    </row>
-    <row r="20" spans="3:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C20" s="18" t="s">
+    </row>
+    <row r="20" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C20" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="E20" s="68"/>
-      <c r="F20" s="68"/>
-    </row>
-    <row r="21" spans="3:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C21" s="18" t="s">
+    </row>
+    <row r="21" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C21" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="24">
         <v>987654321</v>
       </c>
-      <c r="E21" s="68"/>
-      <c r="F21" s="68"/>
-    </row>
-    <row r="22" spans="3:6" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="E22" s="21"/>
-      <c r="F22" s="68"/>
-    </row>
-    <row r="23" spans="3:6" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="C23" s="6" t="s">
+    </row>
+    <row r="22" spans="3:5" ht="19.5" x14ac:dyDescent="0.45">
+      <c r="E22" s="17"/>
+    </row>
+    <row r="23" spans="3:5" ht="19.5" x14ac:dyDescent="0.45">
+      <c r="C23" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="68"/>
-    </row>
-    <row r="24" spans="3:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C24" s="19"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="68"/>
-    </row>
-    <row r="25" spans="3:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C25" s="18" t="s">
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C24" s="15"/>
+      <c r="D24" s="16"/>
+    </row>
+    <row r="25" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C25" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="25">
         <v>8131713388</v>
       </c>
-      <c r="E25" s="68"/>
-      <c r="F25" s="68"/>
-    </row>
-    <row r="26" spans="3:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C26" s="18" t="s">
+    </row>
+    <row r="26" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C26" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="26">
         <v>81931713388</v>
       </c>
-      <c r="E26" s="68"/>
-      <c r="F26" s="68"/>
-    </row>
-    <row r="27" spans="3:6" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="C27" s="18" t="s">
+    </row>
+    <row r="27" spans="3:5" ht="19.5" x14ac:dyDescent="0.45">
+      <c r="C27" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D27" s="31" t="s">
+      <c r="D27" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="E27" s="21"/>
-      <c r="F27" s="68"/>
-    </row>
-    <row r="28" spans="3:6" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="E28" s="21"/>
-      <c r="F28" s="68"/>
-    </row>
-    <row r="29" spans="3:6" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="C29" s="6" t="s">
+      <c r="E27" s="17"/>
+    </row>
+    <row r="28" spans="3:5" ht="19.5" x14ac:dyDescent="0.45">
+      <c r="E28" s="17"/>
+    </row>
+    <row r="29" spans="3:5" ht="19.5" x14ac:dyDescent="0.45">
+      <c r="C29" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="D29" s="6"/>
-      <c r="E29" s="68"/>
-      <c r="F29" s="68"/>
-    </row>
-    <row r="30" spans="3:6" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="68"/>
-    </row>
-    <row r="31" spans="3:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C31" s="18" t="s">
+      <c r="D29" s="4"/>
+    </row>
+    <row r="30" spans="3:5" ht="19.5" x14ac:dyDescent="0.45">
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+    </row>
+    <row r="31" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C31" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D31" s="25" t="s">
+      <c r="D31" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="E31" s="68"/>
-      <c r="F31" s="68"/>
-    </row>
-    <row r="32" spans="3:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C32" s="18" t="s">
+    </row>
+    <row r="32" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C32" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="D32" s="25" t="s">
+      <c r="D32" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="68"/>
-      <c r="F32" s="68"/>
-    </row>
-    <row r="33" spans="3:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C33" s="18" t="s">
+    </row>
+    <row r="33" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C33" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="D33" s="25" t="s">
+      <c r="D33" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="68"/>
-      <c r="F33" s="68"/>
-    </row>
-    <row r="34" spans="3:6" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="C34" s="18" t="s">
+    </row>
+    <row r="34" spans="3:5" ht="19.5" x14ac:dyDescent="0.45">
+      <c r="C34" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D34" s="25" t="s">
+      <c r="D34" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="21"/>
-      <c r="F34" s="68"/>
-    </row>
-    <row r="35" spans="3:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C35" s="18" t="s">
+      <c r="E34" s="17"/>
+    </row>
+    <row r="35" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C35" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="25" t="s">
+      <c r="D35" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="E35" s="68"/>
-      <c r="F35" s="68"/>
-    </row>
-    <row r="36" spans="3:6" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="E36" s="21"/>
-      <c r="F36" s="68"/>
-    </row>
-    <row r="37" spans="3:6" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="C37" s="6" t="s">
+    </row>
+    <row r="36" spans="3:5" ht="19.5" x14ac:dyDescent="0.45">
+      <c r="E36" s="17"/>
+    </row>
+    <row r="37" spans="3:5" ht="19.5" x14ac:dyDescent="0.45">
+      <c r="C37" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="D37" s="6"/>
-    </row>
-    <row r="38" spans="3:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C38" s="18" t="s">
+      <c r="D37" s="4"/>
+    </row>
+    <row r="38" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C38" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="D38" s="22" t="s">
+      <c r="D38" s="18" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C39" s="18" t="s">
+    <row r="39" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C39" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D39" s="23">
+      <c r="D39" s="19">
         <v>32112312398</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C40" s="18" t="s">
+    <row r="40" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C40" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D40" s="24">
+      <c r="D40" s="20">
         <v>45563</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C41" s="18" t="s">
+    <row r="41" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C41" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D41" s="25" t="s">
+      <c r="D41" s="21" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C42" s="18" t="s">
+    <row r="42" spans="3:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C42" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="D42" s="25" t="s">
+      <c r="D42" s="21" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="43" spans="3:6" x14ac:dyDescent="0.35"/>
-    <row r="44" spans="3:6" x14ac:dyDescent="0.35"/>
-    <row r="45" spans="3:6" x14ac:dyDescent="0.35"/>
-    <row r="46" spans="3:6" x14ac:dyDescent="0.35"/>
-    <row r="47" spans="3:6" x14ac:dyDescent="0.35"/>
-    <row r="48" spans="3:6" x14ac:dyDescent="0.35"/>
+    <row r="43" spans="3:5" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="3:5" x14ac:dyDescent="0.35"/>
+    <row r="45" spans="3:5" x14ac:dyDescent="0.35"/>
+    <row r="46" spans="3:5" x14ac:dyDescent="0.35"/>
+    <row r="47" spans="3:5" x14ac:dyDescent="0.35"/>
+    <row r="48" spans="3:5" x14ac:dyDescent="0.35"/>
     <row r="49" x14ac:dyDescent="0.35"/>
     <row r="50" x14ac:dyDescent="0.35"/>
     <row r="51" x14ac:dyDescent="0.35"/>
@@ -24656,7 +24615,7 @@
     <row r="53" x14ac:dyDescent="0.35"/>
     <row r="54" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <sheetProtection sheet="1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D31:D35" xr:uid="{98B6C0F3-0364-48E4-B0C1-58B64AF4E87E}">
       <formula1>"SIM,NÃO"</formula1>
@@ -24687,321 +24646,321 @@
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.90625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="42.26953125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="43.26953125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="1.90625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="14.81640625" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="8.7265625" style="5" hidden="1"/>
+    <col min="1" max="1" width="29.90625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.7265625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="42.26953125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="43.26953125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="1.90625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="8.7265625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.81640625" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="3" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:7" x14ac:dyDescent="0.35"/>
     <row r="2" spans="3:7" x14ac:dyDescent="0.35"/>
     <row r="3" spans="3:7" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="34" t="s">
         <v>242</v>
       </c>
-      <c r="D4" s="38"/>
+      <c r="D4" s="34"/>
     </row>
     <row r="5" spans="3:7" x14ac:dyDescent="0.35"/>
     <row r="6" spans="3:7" x14ac:dyDescent="0.35"/>
     <row r="7" spans="3:7" ht="26" x14ac:dyDescent="0.6">
-      <c r="F7" s="1">
+      <c r="F7" s="89">
         <f>SUM(D19,D32,D45)</f>
         <v>25971.35</v>
       </c>
-      <c r="G7" s="2"/>
+      <c r="G7" s="90"/>
     </row>
     <row r="8" spans="3:7" x14ac:dyDescent="0.35"/>
     <row r="9" spans="3:7" x14ac:dyDescent="0.35"/>
     <row r="10" spans="3:7" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C10" s="7"/>
+      <c r="C10" s="5"/>
     </row>
     <row r="11" spans="3:7" x14ac:dyDescent="0.35"/>
     <row r="12" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="3:7" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="18" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="3:7" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="18" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="15" spans="3:7" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="32">
+      <c r="D15" s="28">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="3:7" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="29">
         <v>123456789</v>
       </c>
     </row>
     <row r="17" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="18">
         <v>2025</v>
       </c>
     </row>
     <row r="18" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="30">
         <v>2850</v>
       </c>
     </row>
     <row r="19" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="30">
         <v>5430.75</v>
       </c>
     </row>
     <row r="20" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="18" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="21" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D21" s="10" t="str">
+      <c r="D21" s="8" t="str">
         <f>IF(OR(D13="",D14="",D15="",D16="",D17="",D18="",D19="",D20=""),"INCOMPLETO",IF(D20="SIM","CONCLUÍDO","PENDENTE"))</f>
         <v>CONCLUÍDO</v>
       </c>
     </row>
     <row r="22" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="18" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="23" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="18" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.35"/>
     <row r="25" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="D26" s="18" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="27" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="D27" s="18" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="28" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="28">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="D29" s="33" t="s">
+      <c r="D29" s="29" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="30" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="18">
         <v>2025</v>
       </c>
     </row>
     <row r="31" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="30">
         <v>4500</v>
       </c>
     </row>
     <row r="32" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D32" s="34">
+      <c r="D32" s="30">
         <v>7890.2</v>
       </c>
     </row>
     <row r="33" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D33" s="22"/>
+      <c r="D33" s="18"/>
     </row>
     <row r="34" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D34" s="10" t="str">
+      <c r="D34" s="8" t="str">
         <f>IF(OR(D26="",D27="",D28="",D29="",D30="",D31="",D32="",D33=""),"INCOMPLETO",IF(D33="SIM","CONCLUÍDO","PENDENTE"))</f>
         <v>INCOMPLETO</v>
       </c>
     </row>
     <row r="35" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D35" s="22"/>
+      <c r="D35" s="18"/>
     </row>
     <row r="36" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D36" s="22" t="s">
+      <c r="D36" s="18" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.35"/>
     <row r="38" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="39" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="22" t="s">
+      <c r="D39" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="40" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D40" s="22" t="s">
+      <c r="D40" s="18" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="41" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D41" s="32">
+      <c r="D41" s="28">
         <v>1234</v>
       </c>
     </row>
     <row r="42" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="D42" s="33">
+      <c r="D42" s="29">
         <v>987654321</v>
       </c>
     </row>
     <row r="43" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D43" s="22">
+      <c r="D43" s="18">
         <v>2025</v>
       </c>
     </row>
     <row r="44" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C44" s="9" t="s">
+      <c r="C44" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="D44" s="34">
+      <c r="D44" s="30">
         <v>8200</v>
       </c>
     </row>
     <row r="45" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C45" s="9" t="s">
+      <c r="C45" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D45" s="34">
+      <c r="D45" s="30">
         <v>12650.4</v>
       </c>
     </row>
     <row r="46" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C46" s="9" t="s">
+      <c r="C46" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D46" s="22" t="s">
+      <c r="D46" s="18" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="47" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C47" s="9" t="s">
+      <c r="C47" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D47" s="10" t="str">
+      <c r="D47" s="8" t="str">
         <f>IF(OR(D39="",D40="",D41="",D42="",D43="",D44="",D45="",D46=""),"INCOMPLETO",IF(D46="SIM","CONCLUÍDO","PENDENTE"))</f>
         <v>PENDENTE</v>
       </c>
     </row>
     <row r="48" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C48" s="9" t="s">
+      <c r="C48" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D48" s="22"/>
+      <c r="D48" s="18"/>
     </row>
     <row r="49" spans="3:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D49" s="22" t="s">
+      <c r="D49" s="18" t="s">
         <v>111</v>
       </c>
     </row>
@@ -25011,7 +24970,7 @@
     <row r="53" spans="3:4" x14ac:dyDescent="0.35"/>
     <row r="54" spans="3:4" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <sheetProtection sheet="1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="F7:G7"/>
   </mergeCells>
@@ -25078,745 +25037,745 @@
   <dimension ref="A1:M54"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.90625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="22.81640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="13.7265625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="16.90625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="12.08984375" style="5" customWidth="1"/>
-    <col min="8" max="8" width="9.36328125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="15" style="5" customWidth="1"/>
-    <col min="10" max="10" width="8.7265625" style="5" customWidth="1"/>
-    <col min="11" max="11" width="9" style="5" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="11.36328125" style="35" hidden="1"/>
-    <col min="13" max="16384" width="8.7265625" style="5" hidden="1"/>
+    <col min="1" max="1" width="29.90625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.7265625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="22.81640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.90625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="12.08984375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="9.36328125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="15" style="3" customWidth="1"/>
+    <col min="10" max="10" width="8.7265625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="9" style="3" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.36328125" style="31" hidden="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.7265625" style="3" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="J1" s="66"/>
+      <c r="J1" s="61"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="J2" s="66"/>
+      <c r="J2" s="61"/>
     </row>
     <row r="3" spans="1:13" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="J3" s="36">
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="J3" s="32">
         <f>SUM(G:G)</f>
         <v>27006.3</v>
       </c>
-      <c r="L3" s="89"/>
-      <c r="M3" s="90"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="80"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="J4" s="36">
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="J4" s="32">
         <f>SUM(H:H)</f>
         <v>2250</v>
       </c>
-      <c r="K4" s="90"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="90"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="79"/>
+      <c r="M4" s="80"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="J5" s="39">
+      <c r="J5" s="35">
         <f>COUNTIF(I:I,"PENDENTE")+COUNTIF(I:I,"INCOMPLETO")</f>
         <v>1</v>
       </c>
-      <c r="K5" s="90"/>
-      <c r="L5" s="82"/>
-      <c r="M5" s="90"/>
+      <c r="K5" s="80"/>
+      <c r="L5" s="74"/>
+      <c r="M5" s="80"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="J6" s="66"/>
-      <c r="K6" s="90"/>
-      <c r="L6" s="82"/>
-      <c r="M6" s="90"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="80"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="J7" s="66"/>
-      <c r="K7" s="90"/>
-      <c r="L7" s="82"/>
-      <c r="M7" s="90"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="80"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="80"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="J8" s="66"/>
-      <c r="K8" s="90"/>
-      <c r="L8" s="82"/>
-      <c r="M8" s="90"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="80"/>
+      <c r="L8" s="74"/>
+      <c r="M8" s="80"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="J9" s="66"/>
-      <c r="K9" s="90"/>
-      <c r="L9" s="82"/>
-      <c r="M9" s="90"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="80"/>
+      <c r="L9" s="74"/>
+      <c r="M9" s="80"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="J10" s="90"/>
-      <c r="K10" s="90"/>
-      <c r="L10" s="82"/>
-      <c r="M10" s="90"/>
+      <c r="J10" s="80"/>
+      <c r="K10" s="80"/>
+      <c r="L10" s="74"/>
+      <c r="M10" s="80"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="J11" s="90"/>
-      <c r="K11" s="90"/>
-      <c r="L11" s="82"/>
-      <c r="M11" s="90"/>
-    </row>
-    <row r="12" spans="1:13" s="42" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="41"/>
-      <c r="C12" s="43" t="s">
+      <c r="J11" s="80"/>
+      <c r="K11" s="80"/>
+      <c r="L11" s="74"/>
+      <c r="M11" s="80"/>
+    </row>
+    <row r="12" spans="1:13" s="38" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="37"/>
+      <c r="C12" s="84" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="92"/>
-      <c r="K12" s="92"/>
-      <c r="L12" s="91"/>
-      <c r="M12" s="92"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
+      <c r="J12" s="82"/>
+      <c r="K12" s="82"/>
+      <c r="L12" s="81"/>
+      <c r="M12" s="82"/>
     </row>
     <row r="13" spans="1:13" ht="26" x14ac:dyDescent="0.35">
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="45" t="s">
+      <c r="D13" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="E13" s="45" t="s">
+      <c r="E13" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="F13" s="45" t="s">
+      <c r="F13" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="G13" s="45" t="s">
+      <c r="G13" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="H13" s="45" t="s">
+      <c r="H13" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="I13" s="45" t="s">
+      <c r="I13" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="J13" s="90"/>
-      <c r="K13" s="90"/>
-      <c r="L13" s="82"/>
-      <c r="M13" s="90"/>
+      <c r="J13" s="80"/>
+      <c r="K13" s="80"/>
+      <c r="L13" s="74"/>
+      <c r="M13" s="80"/>
     </row>
     <row r="14" spans="1:13" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C14" s="48">
+      <c r="C14" s="43">
         <v>45662</v>
       </c>
-      <c r="D14" s="49" t="s">
+      <c r="D14" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="E14" s="50">
+      <c r="E14" s="45">
         <v>12345678900</v>
       </c>
-      <c r="F14" s="51" t="s">
+      <c r="F14" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="G14" s="52">
+      <c r="G14" s="47">
         <v>4500</v>
       </c>
-      <c r="H14" s="52">
+      <c r="H14" s="47">
         <v>450</v>
       </c>
-      <c r="I14" s="46" t="str">
+      <c r="I14" s="41" t="str">
         <f>IF(COUNTA(C14:H14)=0,"",IF(OR(C14="",D14="",E14="",F14="",G14="",H14=""),"INCOMPLETO","CONCLUÍDO"))</f>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="J14" s="90"/>
-      <c r="K14" s="90"/>
-      <c r="L14" s="82"/>
-      <c r="M14" s="90"/>
+      <c r="J14" s="80"/>
+      <c r="K14" s="80"/>
+      <c r="L14" s="74"/>
+      <c r="M14" s="80"/>
     </row>
     <row r="15" spans="1:13" ht="16" x14ac:dyDescent="0.35">
-      <c r="C15" s="48">
+      <c r="C15" s="43">
         <v>45663</v>
       </c>
-      <c r="D15" s="49" t="s">
+      <c r="D15" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="45">
         <v>23456789000</v>
       </c>
-      <c r="F15" s="51" t="s">
+      <c r="F15" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="G15" s="52">
+      <c r="G15" s="47">
         <v>4500</v>
       </c>
-      <c r="H15" s="52">
+      <c r="H15" s="47">
         <v>450</v>
       </c>
-      <c r="I15" s="46" t="str">
+      <c r="I15" s="41" t="str">
         <f t="shared" ref="I15:I50" si="0">IF(COUNTA(C15:H15)=0,"",IF(OR(C15="",D15="",E15="",F15="",G15="",H15=""),"INCOMPLETO","CONCLUÍDO"))</f>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="J15" s="90"/>
-      <c r="K15" s="90"/>
-      <c r="L15" s="82"/>
-      <c r="M15" s="90"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="80"/>
+      <c r="L15" s="74"/>
+      <c r="M15" s="80"/>
     </row>
     <row r="16" spans="1:13" ht="16" x14ac:dyDescent="0.35">
-      <c r="C16" s="48">
+      <c r="C16" s="43">
         <v>45664</v>
       </c>
-      <c r="D16" s="49" t="s">
+      <c r="D16" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="45">
         <v>34567890100</v>
       </c>
-      <c r="F16" s="51" t="s">
+      <c r="F16" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="G16" s="52">
+      <c r="G16" s="47">
         <v>4500</v>
       </c>
-      <c r="H16" s="52">
+      <c r="H16" s="47">
         <v>450</v>
       </c>
-      <c r="I16" s="46" t="str">
+      <c r="I16" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="J16" s="90"/>
-      <c r="K16" s="90"/>
-      <c r="L16" s="82"/>
-      <c r="M16" s="90"/>
+      <c r="J16" s="80"/>
+      <c r="K16" s="80"/>
+      <c r="L16" s="74"/>
+      <c r="M16" s="80"/>
     </row>
     <row r="17" spans="3:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="C17" s="48">
+      <c r="C17" s="43">
         <v>45665</v>
       </c>
-      <c r="D17" s="49" t="s">
+      <c r="D17" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="45">
         <v>45678901200</v>
       </c>
-      <c r="F17" s="51" t="s">
+      <c r="F17" s="46" t="s">
         <v>124</v>
       </c>
-      <c r="G17" s="52">
+      <c r="G17" s="47">
         <v>1800</v>
       </c>
-      <c r="H17" s="52">
+      <c r="H17" s="47">
         <v>0</v>
       </c>
-      <c r="I17" s="46" t="str">
+      <c r="I17" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="J17" s="90"/>
-      <c r="K17" s="90"/>
+      <c r="J17" s="80"/>
+      <c r="K17" s="80"/>
     </row>
     <row r="18" spans="3:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="C18" s="48">
+      <c r="C18" s="43">
         <v>45666</v>
       </c>
-      <c r="D18" s="49" t="s">
+      <c r="D18" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="45">
         <v>56789012300</v>
       </c>
-      <c r="F18" s="51" t="s">
+      <c r="F18" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="G18" s="52">
+      <c r="G18" s="47">
         <v>2200</v>
       </c>
-      <c r="H18" s="52">
+      <c r="H18" s="47">
         <v>0</v>
       </c>
-      <c r="I18" s="46" t="str">
+      <c r="I18" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="J18" s="90"/>
-      <c r="K18" s="90"/>
+      <c r="J18" s="80"/>
+      <c r="K18" s="80"/>
     </row>
     <row r="19" spans="3:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="C19" s="48">
+      <c r="C19" s="43">
         <v>45667</v>
       </c>
-      <c r="D19" s="49" t="s">
+      <c r="D19" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="45">
         <v>67890123400</v>
       </c>
-      <c r="F19" s="51" t="s">
+      <c r="F19" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="G19" s="52">
+      <c r="G19" s="47">
         <v>180.5</v>
       </c>
-      <c r="H19" s="52">
+      <c r="H19" s="47">
         <v>0</v>
       </c>
-      <c r="I19" s="46" t="str">
+      <c r="I19" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="J19" s="90"/>
-      <c r="K19" s="90"/>
+      <c r="J19" s="80"/>
+      <c r="K19" s="80"/>
     </row>
     <row r="20" spans="3:11" ht="32" x14ac:dyDescent="0.35">
-      <c r="C20" s="48">
+      <c r="C20" s="43">
         <v>45668</v>
       </c>
-      <c r="D20" s="49" t="s">
+      <c r="D20" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="45">
         <v>78901234500</v>
       </c>
-      <c r="F20" s="51" t="s">
+      <c r="F20" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="G20" s="52">
+      <c r="G20" s="47">
         <v>325.8</v>
       </c>
-      <c r="H20" s="52">
+      <c r="H20" s="47">
         <v>0</v>
       </c>
-      <c r="I20" s="46" t="str">
+      <c r="I20" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="J20" s="90"/>
-      <c r="K20" s="90"/>
+      <c r="J20" s="80"/>
+      <c r="K20" s="80"/>
     </row>
     <row r="21" spans="3:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="C21" s="48">
+      <c r="C21" s="43">
         <v>45669</v>
       </c>
-      <c r="D21" s="49" t="s">
+      <c r="D21" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="45">
         <v>89012345600</v>
       </c>
-      <c r="F21" s="51" t="s">
+      <c r="F21" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="G21" s="52">
+      <c r="G21" s="47">
         <v>4500</v>
       </c>
-      <c r="H21" s="52">
+      <c r="H21" s="47">
         <v>450</v>
       </c>
-      <c r="I21" s="46" t="str">
+      <c r="I21" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="J21" s="90"/>
-      <c r="K21" s="90"/>
+      <c r="J21" s="80"/>
+      <c r="K21" s="80"/>
     </row>
     <row r="22" spans="3:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="C22" s="48">
+      <c r="C22" s="43">
         <v>45670</v>
       </c>
-      <c r="D22" s="49" t="s">
+      <c r="D22" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="45">
         <v>90123456700</v>
       </c>
-      <c r="F22" s="51" t="s">
+      <c r="F22" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="G22" s="52">
+      <c r="G22" s="47">
         <v>4500</v>
       </c>
-      <c r="H22" s="52">
+      <c r="H22" s="47">
         <v>450</v>
       </c>
-      <c r="I22" s="46" t="str">
+      <c r="I22" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="J22" s="90"/>
-      <c r="K22" s="90"/>
+      <c r="J22" s="80"/>
+      <c r="K22" s="80"/>
     </row>
     <row r="23" spans="3:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="C23" s="48">
+      <c r="C23" s="43">
         <v>45671</v>
       </c>
-      <c r="D23" s="49" t="s">
+      <c r="D23" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="45">
         <v>11223344500</v>
       </c>
-      <c r="F23" s="51" t="s">
+      <c r="F23" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="G23" s="51"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="46" t="str">
+      <c r="G23" s="46"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="41" t="str">
         <f t="shared" si="0"/>
         <v>INCOMPLETO</v>
       </c>
-      <c r="J23" s="90"/>
-      <c r="K23" s="90"/>
+      <c r="J23" s="80"/>
+      <c r="K23" s="80"/>
     </row>
     <row r="24" spans="3:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="C24" s="48"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="46" t="str">
+      <c r="C24" s="43"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="25" spans="3:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="C25" s="48"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="46" t="str">
+      <c r="C25" s="43"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="26" spans="3:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="C26" s="51"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="51"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="46" t="str">
+      <c r="C26" s="46"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="27" spans="3:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="C27" s="51"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="46" t="str">
+      <c r="C27" s="46"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="28" spans="3:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="C28" s="51"/>
-      <c r="D28" s="49"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="46" t="str">
+      <c r="C28" s="46"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="29" spans="3:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="C29" s="51"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="46" t="str">
+      <c r="C29" s="46"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="47"/>
+      <c r="I29" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="30" spans="3:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="C30" s="51"/>
-      <c r="D30" s="49"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="46" t="str">
+      <c r="C30" s="46"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="47"/>
+      <c r="I30" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="31" spans="3:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="C31" s="51"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="51"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="46" t="str">
+      <c r="C31" s="46"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="32" spans="3:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="C32" s="51"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="46" t="str">
+      <c r="C32" s="46"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="33" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C33" s="51"/>
-      <c r="D33" s="49"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="51"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="46" t="str">
+      <c r="C33" s="46"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="47"/>
+      <c r="I33" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="34" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C34" s="51"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="51"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="46" t="str">
+      <c r="C34" s="46"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="47"/>
+      <c r="I34" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="35" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C35" s="51"/>
-      <c r="D35" s="49"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="46" t="str">
+      <c r="C35" s="46"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="36" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C36" s="51"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="52"/>
-      <c r="I36" s="46" t="str">
+      <c r="C36" s="46"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="37" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C37" s="51"/>
-      <c r="D37" s="49"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="51"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="52"/>
-      <c r="I37" s="46" t="str">
+      <c r="C37" s="46"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="47"/>
+      <c r="I37" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="38" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C38" s="51"/>
-      <c r="D38" s="49"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="51"/>
-      <c r="G38" s="51"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="46" t="str">
+      <c r="C38" s="46"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="47"/>
+      <c r="I38" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="39" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C39" s="51"/>
-      <c r="D39" s="49"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="51"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="52"/>
-      <c r="I39" s="46" t="str">
+      <c r="C39" s="46"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="46"/>
+      <c r="G39" s="46"/>
+      <c r="H39" s="47"/>
+      <c r="I39" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="40" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C40" s="51"/>
-      <c r="D40" s="49"/>
-      <c r="E40" s="50"/>
-      <c r="F40" s="51"/>
-      <c r="G40" s="51"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="46" t="str">
+      <c r="C40" s="46"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="46"/>
+      <c r="G40" s="46"/>
+      <c r="H40" s="47"/>
+      <c r="I40" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="41" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C41" s="51"/>
-      <c r="D41" s="49"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="51"/>
-      <c r="G41" s="51"/>
-      <c r="H41" s="52"/>
-      <c r="I41" s="46" t="str">
+      <c r="C41" s="46"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="46"/>
+      <c r="G41" s="46"/>
+      <c r="H41" s="47"/>
+      <c r="I41" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="42" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C42" s="51"/>
-      <c r="D42" s="49"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="51"/>
-      <c r="G42" s="51"/>
-      <c r="H42" s="52"/>
-      <c r="I42" s="46" t="str">
+      <c r="C42" s="46"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="46"/>
+      <c r="G42" s="46"/>
+      <c r="H42" s="47"/>
+      <c r="I42" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="43" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C43" s="51"/>
-      <c r="D43" s="49"/>
-      <c r="E43" s="50"/>
-      <c r="F43" s="51"/>
-      <c r="G43" s="51"/>
-      <c r="H43" s="52"/>
-      <c r="I43" s="46" t="str">
+      <c r="C43" s="46"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="46"/>
+      <c r="G43" s="46"/>
+      <c r="H43" s="47"/>
+      <c r="I43" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="44" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C44" s="51"/>
-      <c r="D44" s="49"/>
-      <c r="E44" s="50"/>
-      <c r="F44" s="51"/>
-      <c r="G44" s="51"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="46" t="str">
+      <c r="C44" s="46"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="45"/>
+      <c r="F44" s="46"/>
+      <c r="G44" s="46"/>
+      <c r="H44" s="47"/>
+      <c r="I44" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="45" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C45" s="51"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="50"/>
-      <c r="F45" s="51"/>
-      <c r="G45" s="51"/>
-      <c r="H45" s="52"/>
-      <c r="I45" s="46" t="str">
+      <c r="C45" s="46"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="46"/>
+      <c r="G45" s="46"/>
+      <c r="H45" s="47"/>
+      <c r="I45" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="46" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C46" s="51"/>
-      <c r="D46" s="49"/>
-      <c r="E46" s="50"/>
-      <c r="F46" s="51"/>
-      <c r="G46" s="51"/>
-      <c r="H46" s="52"/>
-      <c r="I46" s="46" t="str">
+      <c r="C46" s="46"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="45"/>
+      <c r="F46" s="46"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="47"/>
+      <c r="I46" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="47" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C47" s="51"/>
-      <c r="D47" s="49"/>
-      <c r="E47" s="50"/>
-      <c r="F47" s="51"/>
-      <c r="G47" s="51"/>
-      <c r="H47" s="52"/>
-      <c r="I47" s="46" t="str">
+      <c r="C47" s="46"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="46"/>
+      <c r="G47" s="46"/>
+      <c r="H47" s="47"/>
+      <c r="I47" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="48" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C48" s="51"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="50"/>
-      <c r="F48" s="51"/>
-      <c r="G48" s="51"/>
-      <c r="H48" s="52"/>
-      <c r="I48" s="46" t="str">
+      <c r="C48" s="46"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="45"/>
+      <c r="F48" s="46"/>
+      <c r="G48" s="46"/>
+      <c r="H48" s="47"/>
+      <c r="I48" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C49" s="51"/>
-      <c r="D49" s="49"/>
-      <c r="E49" s="50"/>
-      <c r="F49" s="51"/>
-      <c r="G49" s="51"/>
-      <c r="H49" s="52"/>
-      <c r="I49" s="46" t="str">
+      <c r="C49" s="46"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="45"/>
+      <c r="F49" s="46"/>
+      <c r="G49" s="46"/>
+      <c r="H49" s="47"/>
+      <c r="I49" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="50" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C50" s="51"/>
-      <c r="D50" s="49"/>
-      <c r="E50" s="50"/>
-      <c r="F50" s="51"/>
-      <c r="G50" s="51"/>
-      <c r="H50" s="52"/>
-      <c r="I50" s="46" t="str">
+      <c r="C50" s="46"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="46"/>
+      <c r="G50" s="46"/>
+      <c r="H50" s="47"/>
+      <c r="I50" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="51" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C51" s="51"/>
-      <c r="D51" s="49"/>
-      <c r="E51" s="53"/>
-      <c r="F51" s="51"/>
-      <c r="G51" s="51"/>
-      <c r="H51" s="52"/>
-      <c r="I51" s="47"/>
+      <c r="C51" s="46"/>
+      <c r="D51" s="44"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="46"/>
+      <c r="G51" s="46"/>
+      <c r="H51" s="47"/>
+      <c r="I51" s="42"/>
     </row>
     <row r="52" spans="3:9" x14ac:dyDescent="0.35"/>
     <row r="53" spans="3:9" x14ac:dyDescent="0.35"/>
     <row r="54" spans="3:9" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <sheetProtection sheet="1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="C12:I12"/>
   </mergeCells>
@@ -25831,18 +25790,14 @@
       <formula>NOT(ISERROR(SEARCH("CONCLUÍDO",I14)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F51" xr:uid="{AF3A6550-2D8D-45FC-A192-BD3E70D096F5}">
       <formula1>ListaRendimentos</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G23:G51" xr:uid="{4AE2472F-7138-41B4-B9CA-A76BB61A17BB}">
       <formula1>"Tributável,Isento e não tributável,Tributação exclusiva/definitiva,Sujeito à tributação no exterior,A verificar"</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Essa faixa é apenas uma validação inicial. Depois podemos ajustá-la para aceitar somente datas do ano-calendário correspondente." sqref="C15:C23" xr:uid="{49D4D280-9DAB-4378-AD77-77C10D9ED9E7}">
-      <formula1>43831</formula1>
-      <formula2>49674</formula2>
-    </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{AAADC016-DFB5-4D80-A21F-672F71120EA0}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14:C51" xr:uid="{AAADC016-DFB5-4D80-A21F-672F71120EA0}">
       <formula1>43831</formula1>
       <formula2>49674</formula2>
     </dataValidation>
@@ -25873,945 +25828,945 @@
   <dimension ref="A1:XFC54"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.90625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="22.81640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="13.7265625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="11.54296875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="12.08984375" style="60" customWidth="1"/>
-    <col min="8" max="8" width="14.6328125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="15" style="5" customWidth="1"/>
-    <col min="10" max="10" width="8.7265625" style="5" customWidth="1"/>
-    <col min="11" max="11" width="6" style="5" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="8.81640625" style="35" hidden="1" customWidth="1"/>
-    <col min="13" max="16383" width="8.7265625" style="5" hidden="1"/>
-    <col min="16384" max="16384" width="6" style="5" hidden="1"/>
+    <col min="1" max="1" width="29.90625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.7265625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="22.81640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="11.54296875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="12.08984375" style="55" customWidth="1"/>
+    <col min="8" max="8" width="14.6328125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="15" style="3" customWidth="1"/>
+    <col min="10" max="10" width="8.7265625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="6" style="3" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="8.81640625" style="31" hidden="1" customWidth="1"/>
+    <col min="13" max="16383" width="8.7265625" style="3" hidden="1"/>
+    <col min="16384" max="16384" width="6" style="3" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="G1" s="5"/>
+      <c r="G1" s="3"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="G2" s="5"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:21" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="J3" s="58">
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="J3" s="53">
         <f>SUM(G:G)</f>
         <v>7570</v>
       </c>
-      <c r="K3" s="90"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="90"/>
-      <c r="O3" s="90"/>
-      <c r="P3" s="90"/>
-      <c r="Q3" s="90"/>
-      <c r="R3" s="90"/>
-      <c r="S3" s="90"/>
-      <c r="T3" s="90"/>
-      <c r="U3" s="90"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="80"/>
+      <c r="U3" s="80"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="G4" s="5"/>
-      <c r="J4" s="58">
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="G4" s="3"/>
+      <c r="J4" s="53">
         <f>SUM(H:H)</f>
         <v>850</v>
       </c>
-      <c r="K4" s="90"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="90"/>
-      <c r="N4" s="90"/>
-      <c r="O4" s="90"/>
-      <c r="P4" s="90"/>
-      <c r="Q4" s="90"/>
-      <c r="R4" s="90"/>
-      <c r="S4" s="90"/>
-      <c r="T4" s="90"/>
-      <c r="U4" s="90"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="79"/>
+      <c r="M4" s="80"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="80"/>
+      <c r="R4" s="80"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="80"/>
+      <c r="U4" s="80"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="G5" s="5"/>
-      <c r="J5" s="39">
+      <c r="G5" s="3"/>
+      <c r="J5" s="35">
         <f>COUNTIF(I:I,"PENDENTE")+COUNTIF(I:I,"INCOMPLETO")</f>
         <v>0</v>
       </c>
-      <c r="K5" s="90"/>
-      <c r="L5" s="82"/>
-      <c r="M5" s="90"/>
-      <c r="N5" s="90"/>
-      <c r="O5" s="90"/>
-      <c r="P5" s="90"/>
-      <c r="Q5" s="90"/>
-      <c r="R5" s="90"/>
-      <c r="S5" s="90"/>
-      <c r="T5" s="90"/>
-      <c r="U5" s="90"/>
+      <c r="K5" s="80"/>
+      <c r="L5" s="74"/>
+      <c r="M5" s="80"/>
+      <c r="N5" s="80"/>
+      <c r="O5" s="80"/>
+      <c r="P5" s="80"/>
+      <c r="Q5" s="80"/>
+      <c r="R5" s="80"/>
+      <c r="S5" s="80"/>
+      <c r="T5" s="80"/>
+      <c r="U5" s="80"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="G6" s="5"/>
-      <c r="K6" s="90"/>
-      <c r="L6" s="82"/>
-      <c r="M6" s="90"/>
-      <c r="N6" s="90"/>
-      <c r="O6" s="90"/>
-      <c r="P6" s="90"/>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90"/>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
+      <c r="G6" s="3"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="80"/>
+      <c r="O6" s="80"/>
+      <c r="P6" s="80"/>
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="G7" s="5"/>
-      <c r="K7" s="90"/>
-      <c r="L7" s="82"/>
-      <c r="M7" s="90"/>
-      <c r="N7" s="90"/>
-      <c r="O7" s="90"/>
-      <c r="P7" s="90"/>
-      <c r="Q7" s="90"/>
-      <c r="R7" s="90"/>
-      <c r="S7" s="90"/>
-      <c r="T7" s="90"/>
-      <c r="U7" s="90"/>
+      <c r="G7" s="3"/>
+      <c r="K7" s="80"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="80"/>
+      <c r="N7" s="80"/>
+      <c r="O7" s="80"/>
+      <c r="P7" s="80"/>
+      <c r="Q7" s="80"/>
+      <c r="R7" s="80"/>
+      <c r="S7" s="80"/>
+      <c r="T7" s="80"/>
+      <c r="U7" s="80"/>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="G8" s="5"/>
-      <c r="K8" s="90"/>
-      <c r="L8" s="82"/>
-      <c r="M8" s="90"/>
-      <c r="N8" s="90"/>
-      <c r="O8" s="90"/>
-      <c r="P8" s="90"/>
-      <c r="Q8" s="90"/>
-      <c r="R8" s="90"/>
-      <c r="S8" s="90"/>
-      <c r="T8" s="90"/>
-      <c r="U8" s="90"/>
+      <c r="G8" s="3"/>
+      <c r="K8" s="80"/>
+      <c r="L8" s="74"/>
+      <c r="M8" s="80"/>
+      <c r="N8" s="80"/>
+      <c r="O8" s="80"/>
+      <c r="P8" s="80"/>
+      <c r="Q8" s="80"/>
+      <c r="R8" s="80"/>
+      <c r="S8" s="80"/>
+      <c r="T8" s="80"/>
+      <c r="U8" s="80"/>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="G9" s="5"/>
-      <c r="K9" s="90"/>
-      <c r="L9" s="82"/>
-      <c r="M9" s="90"/>
-      <c r="N9" s="90"/>
-      <c r="O9" s="90"/>
-      <c r="P9" s="90"/>
-      <c r="Q9" s="90"/>
-      <c r="R9" s="90"/>
-      <c r="S9" s="90"/>
-      <c r="T9" s="90"/>
-      <c r="U9" s="90"/>
+      <c r="G9" s="3"/>
+      <c r="K9" s="80"/>
+      <c r="L9" s="74"/>
+      <c r="M9" s="80"/>
+      <c r="N9" s="80"/>
+      <c r="O9" s="80"/>
+      <c r="P9" s="80"/>
+      <c r="Q9" s="80"/>
+      <c r="R9" s="80"/>
+      <c r="S9" s="80"/>
+      <c r="T9" s="80"/>
+      <c r="U9" s="80"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="G10" s="5"/>
-      <c r="K10" s="90"/>
-      <c r="L10" s="82"/>
-      <c r="M10" s="90"/>
-      <c r="N10" s="90"/>
-      <c r="O10" s="90"/>
-      <c r="P10" s="90"/>
-      <c r="Q10" s="90"/>
-      <c r="R10" s="90"/>
-      <c r="S10" s="90"/>
-      <c r="T10" s="90"/>
-      <c r="U10" s="90"/>
+      <c r="G10" s="3"/>
+      <c r="K10" s="80"/>
+      <c r="L10" s="74"/>
+      <c r="M10" s="80"/>
+      <c r="N10" s="80"/>
+      <c r="O10" s="80"/>
+      <c r="P10" s="80"/>
+      <c r="Q10" s="80"/>
+      <c r="R10" s="80"/>
+      <c r="S10" s="80"/>
+      <c r="T10" s="80"/>
+      <c r="U10" s="80"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="G11" s="5"/>
-      <c r="K11" s="90"/>
-      <c r="L11" s="82"/>
-      <c r="M11" s="90"/>
-      <c r="N11" s="90"/>
-      <c r="O11" s="90"/>
-      <c r="P11" s="90"/>
-      <c r="Q11" s="90"/>
-      <c r="R11" s="90"/>
-      <c r="S11" s="90"/>
-      <c r="T11" s="90"/>
-      <c r="U11" s="90"/>
-    </row>
-    <row r="12" spans="1:21" s="42" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="41"/>
-      <c r="C12" s="43" t="s">
+      <c r="G11" s="3"/>
+      <c r="K11" s="80"/>
+      <c r="L11" s="74"/>
+      <c r="M11" s="80"/>
+      <c r="N11" s="80"/>
+      <c r="O11" s="80"/>
+      <c r="P11" s="80"/>
+      <c r="Q11" s="80"/>
+      <c r="R11" s="80"/>
+      <c r="S11" s="80"/>
+      <c r="T11" s="80"/>
+      <c r="U11" s="80"/>
+    </row>
+    <row r="12" spans="1:21" s="38" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="37"/>
+      <c r="C12" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="K12" s="92"/>
-      <c r="L12" s="91"/>
-      <c r="M12" s="92"/>
-      <c r="N12" s="92"/>
-      <c r="O12" s="92"/>
-      <c r="P12" s="92"/>
-      <c r="Q12" s="92"/>
-      <c r="R12" s="92"/>
-      <c r="S12" s="92"/>
-      <c r="T12" s="92"/>
-      <c r="U12" s="92"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
+      <c r="K12" s="82"/>
+      <c r="L12" s="81"/>
+      <c r="M12" s="82"/>
+      <c r="N12" s="82"/>
+      <c r="O12" s="82"/>
+      <c r="P12" s="82"/>
+      <c r="Q12" s="82"/>
+      <c r="R12" s="82"/>
+      <c r="S12" s="82"/>
+      <c r="T12" s="82"/>
+      <c r="U12" s="82"/>
     </row>
     <row r="13" spans="1:21" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="45" t="s">
+      <c r="D13" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="E13" s="45" t="s">
+      <c r="E13" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="F13" s="45" t="s">
+      <c r="F13" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="G13" s="45" t="s">
+      <c r="G13" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="H13" s="45" t="s">
+      <c r="H13" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="I13" s="45" t="s">
+      <c r="I13" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="K13" s="90"/>
-      <c r="L13" s="82"/>
-      <c r="M13" s="90"/>
-      <c r="N13" s="90"/>
-      <c r="O13" s="90"/>
-      <c r="P13" s="90"/>
-      <c r="Q13" s="90"/>
-      <c r="R13" s="90"/>
-      <c r="S13" s="90"/>
-      <c r="T13" s="90"/>
-      <c r="U13" s="90"/>
+      <c r="K13" s="80"/>
+      <c r="L13" s="74"/>
+      <c r="M13" s="80"/>
+      <c r="N13" s="80"/>
+      <c r="O13" s="80"/>
+      <c r="P13" s="80"/>
+      <c r="Q13" s="80"/>
+      <c r="R13" s="80"/>
+      <c r="S13" s="80"/>
+      <c r="T13" s="80"/>
+      <c r="U13" s="80"/>
     </row>
     <row r="14" spans="1:21" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C14" s="48">
+      <c r="C14" s="43">
         <v>45662</v>
       </c>
-      <c r="D14" s="49" t="s">
+      <c r="D14" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="E14" s="50">
+      <c r="E14" s="45">
         <v>12345678900</v>
       </c>
-      <c r="F14" s="54" t="s">
+      <c r="F14" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="52">
+      <c r="G14" s="47">
         <v>350</v>
       </c>
-      <c r="H14" s="52">
+      <c r="H14" s="47">
         <v>0</v>
       </c>
-      <c r="I14" s="46" t="str">
-        <f>IF(COUNTA(C14:H14)=0,"",IF(OR(C14="",D14="",E14="",F14="",G14="",H14=""),"INCOMPLETO","CONCLUÍDO"))</f>
+      <c r="I14" s="41" t="str">
+        <f>IF(COUNTA(C14:H14)=0,"",IF(OR(C14="",D14="",E14="",F14="",G14=""),"INCOMPLETO","CONCLUÍDO"))</f>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="K14" s="90"/>
-      <c r="L14" s="82"/>
-      <c r="M14" s="90"/>
-      <c r="N14" s="90"/>
-      <c r="O14" s="90"/>
-      <c r="P14" s="90"/>
-      <c r="Q14" s="90"/>
-      <c r="R14" s="90"/>
-      <c r="S14" s="90"/>
-      <c r="T14" s="90"/>
-      <c r="U14" s="90"/>
+      <c r="K14" s="80"/>
+      <c r="L14" s="74"/>
+      <c r="M14" s="80"/>
+      <c r="N14" s="80"/>
+      <c r="O14" s="80"/>
+      <c r="P14" s="80"/>
+      <c r="Q14" s="80"/>
+      <c r="R14" s="80"/>
+      <c r="S14" s="80"/>
+      <c r="T14" s="80"/>
+      <c r="U14" s="80"/>
     </row>
     <row r="15" spans="1:21" ht="16" x14ac:dyDescent="0.35">
-      <c r="C15" s="48">
+      <c r="C15" s="43">
         <v>45669</v>
       </c>
-      <c r="D15" s="49" t="s">
+      <c r="D15" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="45">
         <v>23456789000</v>
       </c>
-      <c r="F15" s="54" t="s">
+      <c r="F15" s="49" t="s">
         <v>138</v>
       </c>
-      <c r="G15" s="52">
+      <c r="G15" s="47">
         <v>420</v>
       </c>
-      <c r="H15" s="52">
+      <c r="H15" s="47">
         <v>200</v>
       </c>
-      <c r="I15" s="46" t="str">
-        <f t="shared" ref="I15:I50" si="0">IF(COUNTA(C15:H15)=0,"",IF(OR(C15="",D15="",E15="",F15="",G15="",H15=""),"INCOMPLETO","CONCLUÍDO"))</f>
+      <c r="I15" s="41" t="str">
+        <f t="shared" ref="I15:I50" si="0">IF(COUNTA(C15:H15)=0,"",IF(OR(C15="",D15="",E15="",F15="",G15=""),"INCOMPLETO","CONCLUÍDO"))</f>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="K15" s="90"/>
-      <c r="L15" s="82"/>
-      <c r="M15" s="90"/>
-      <c r="N15" s="90"/>
-      <c r="O15" s="90"/>
-      <c r="P15" s="90"/>
-      <c r="Q15" s="90"/>
-      <c r="R15" s="90"/>
-      <c r="S15" s="90"/>
-      <c r="T15" s="90"/>
-      <c r="U15" s="90"/>
+      <c r="K15" s="80"/>
+      <c r="L15" s="74"/>
+      <c r="M15" s="80"/>
+      <c r="N15" s="80"/>
+      <c r="O15" s="80"/>
+      <c r="P15" s="80"/>
+      <c r="Q15" s="80"/>
+      <c r="R15" s="80"/>
+      <c r="S15" s="80"/>
+      <c r="T15" s="80"/>
+      <c r="U15" s="80"/>
     </row>
     <row r="16" spans="1:21" ht="16" x14ac:dyDescent="0.35">
-      <c r="C16" s="48">
+      <c r="C16" s="43">
         <v>45708</v>
       </c>
-      <c r="D16" s="49" t="s">
+      <c r="D16" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="45">
         <v>34567890100</v>
       </c>
-      <c r="F16" s="54" t="s">
+      <c r="F16" s="49" t="s">
         <v>143</v>
       </c>
-      <c r="G16" s="52">
+      <c r="G16" s="47">
         <v>680</v>
       </c>
-      <c r="H16" s="52">
+      <c r="H16" s="47">
         <v>0</v>
       </c>
-      <c r="I16" s="46" t="str">
+      <c r="I16" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="K16" s="90"/>
-      <c r="L16" s="82"/>
-      <c r="M16" s="90"/>
-      <c r="N16" s="90"/>
-      <c r="O16" s="90"/>
-      <c r="P16" s="90"/>
-      <c r="Q16" s="90"/>
-      <c r="R16" s="90"/>
-      <c r="S16" s="90"/>
-      <c r="T16" s="90"/>
-      <c r="U16" s="90"/>
+      <c r="K16" s="80"/>
+      <c r="L16" s="74"/>
+      <c r="M16" s="80"/>
+      <c r="N16" s="80"/>
+      <c r="O16" s="80"/>
+      <c r="P16" s="80"/>
+      <c r="Q16" s="80"/>
+      <c r="R16" s="80"/>
+      <c r="S16" s="80"/>
+      <c r="T16" s="80"/>
+      <c r="U16" s="80"/>
     </row>
     <row r="17" spans="3:21" ht="16" x14ac:dyDescent="0.35">
-      <c r="C17" s="48">
+      <c r="C17" s="43">
         <v>45721</v>
       </c>
-      <c r="D17" s="49" t="s">
+      <c r="D17" s="44" t="s">
         <v>144</v>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="45">
         <v>45678901200</v>
       </c>
-      <c r="F17" s="54" t="s">
+      <c r="F17" s="49" t="s">
         <v>145</v>
       </c>
-      <c r="G17" s="52">
+      <c r="G17" s="47">
         <v>1250</v>
       </c>
-      <c r="H17" s="52">
+      <c r="H17" s="47">
         <v>0</v>
       </c>
-      <c r="I17" s="46" t="str">
+      <c r="I17" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="K17" s="90"/>
-      <c r="L17" s="82"/>
-      <c r="M17" s="90"/>
-      <c r="N17" s="90"/>
-      <c r="O17" s="90"/>
-      <c r="P17" s="90"/>
-      <c r="Q17" s="90"/>
-      <c r="R17" s="90"/>
-      <c r="S17" s="90"/>
-      <c r="T17" s="90"/>
-      <c r="U17" s="90"/>
+      <c r="K17" s="80"/>
+      <c r="L17" s="74"/>
+      <c r="M17" s="80"/>
+      <c r="N17" s="80"/>
+      <c r="O17" s="80"/>
+      <c r="P17" s="80"/>
+      <c r="Q17" s="80"/>
+      <c r="R17" s="80"/>
+      <c r="S17" s="80"/>
+      <c r="T17" s="80"/>
+      <c r="U17" s="80"/>
     </row>
     <row r="18" spans="3:21" ht="16" x14ac:dyDescent="0.35">
-      <c r="C18" s="48">
+      <c r="C18" s="43">
         <v>45730</v>
       </c>
-      <c r="D18" s="49" t="s">
+      <c r="D18" s="44" t="s">
         <v>146</v>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="45">
         <v>56789012300</v>
       </c>
-      <c r="F18" s="54" t="s">
+      <c r="F18" s="49" t="s">
         <v>147</v>
       </c>
-      <c r="G18" s="52">
+      <c r="G18" s="47">
         <v>240</v>
       </c>
-      <c r="H18" s="52">
+      <c r="H18" s="47">
         <v>0</v>
       </c>
-      <c r="I18" s="46" t="str">
+      <c r="I18" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="K18" s="90"/>
-      <c r="L18" s="82"/>
-      <c r="M18" s="90"/>
-      <c r="N18" s="90"/>
-      <c r="O18" s="90"/>
-      <c r="P18" s="90"/>
-      <c r="Q18" s="90"/>
-      <c r="R18" s="90"/>
-      <c r="S18" s="90"/>
-      <c r="T18" s="90"/>
-      <c r="U18" s="90"/>
+      <c r="K18" s="80"/>
+      <c r="L18" s="74"/>
+      <c r="M18" s="80"/>
+      <c r="N18" s="80"/>
+      <c r="O18" s="80"/>
+      <c r="P18" s="80"/>
+      <c r="Q18" s="80"/>
+      <c r="R18" s="80"/>
+      <c r="S18" s="80"/>
+      <c r="T18" s="80"/>
+      <c r="U18" s="80"/>
     </row>
     <row r="19" spans="3:21" ht="16" x14ac:dyDescent="0.35">
-      <c r="C19" s="48">
+      <c r="C19" s="43">
         <v>45756</v>
       </c>
-      <c r="D19" s="49" t="s">
+      <c r="D19" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="45">
         <v>67890123400</v>
       </c>
-      <c r="F19" s="54" t="s">
+      <c r="F19" s="49" t="s">
         <v>149</v>
       </c>
-      <c r="G19" s="52">
+      <c r="G19" s="47">
         <v>1850</v>
       </c>
-      <c r="H19" s="52">
+      <c r="H19" s="47">
         <v>650</v>
       </c>
-      <c r="I19" s="46" t="str">
+      <c r="I19" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="K19" s="90"/>
-      <c r="L19" s="82"/>
-      <c r="M19" s="90"/>
-      <c r="N19" s="90"/>
-      <c r="O19" s="90"/>
-      <c r="P19" s="90"/>
-      <c r="Q19" s="90"/>
-      <c r="R19" s="90"/>
-      <c r="S19" s="90"/>
-      <c r="T19" s="90"/>
-      <c r="U19" s="90"/>
+      <c r="K19" s="80"/>
+      <c r="L19" s="74"/>
+      <c r="M19" s="80"/>
+      <c r="N19" s="80"/>
+      <c r="O19" s="80"/>
+      <c r="P19" s="80"/>
+      <c r="Q19" s="80"/>
+      <c r="R19" s="80"/>
+      <c r="S19" s="80"/>
+      <c r="T19" s="80"/>
+      <c r="U19" s="80"/>
     </row>
     <row r="20" spans="3:21" ht="16" x14ac:dyDescent="0.35">
-      <c r="C20" s="48">
+      <c r="C20" s="43">
         <v>45792</v>
       </c>
-      <c r="D20" s="49" t="s">
+      <c r="D20" s="44" t="s">
         <v>150</v>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="45">
         <v>78901234500</v>
       </c>
-      <c r="F20" s="54" t="s">
+      <c r="F20" s="49" t="s">
         <v>151</v>
       </c>
-      <c r="G20" s="52">
+      <c r="G20" s="47">
         <v>580</v>
       </c>
-      <c r="H20" s="52">
+      <c r="H20" s="47">
         <v>0</v>
       </c>
-      <c r="I20" s="46" t="str">
+      <c r="I20" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="K20" s="90"/>
-      <c r="L20" s="82"/>
-      <c r="M20" s="90"/>
-      <c r="N20" s="90"/>
-      <c r="O20" s="90"/>
-      <c r="P20" s="90"/>
-      <c r="Q20" s="90"/>
-      <c r="R20" s="90"/>
-      <c r="S20" s="90"/>
-      <c r="T20" s="90"/>
-      <c r="U20" s="90"/>
+      <c r="K20" s="80"/>
+      <c r="L20" s="74"/>
+      <c r="M20" s="80"/>
+      <c r="N20" s="80"/>
+      <c r="O20" s="80"/>
+      <c r="P20" s="80"/>
+      <c r="Q20" s="80"/>
+      <c r="R20" s="80"/>
+      <c r="S20" s="80"/>
+      <c r="T20" s="80"/>
+      <c r="U20" s="80"/>
     </row>
     <row r="21" spans="3:21" ht="16" x14ac:dyDescent="0.35">
-      <c r="C21" s="48">
+      <c r="C21" s="43">
         <v>45818</v>
       </c>
-      <c r="D21" s="49" t="s">
+      <c r="D21" s="44" t="s">
         <v>144</v>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="45">
         <v>89012345600</v>
       </c>
-      <c r="F21" s="54" t="s">
+      <c r="F21" s="49" t="s">
         <v>145</v>
       </c>
-      <c r="G21" s="52">
+      <c r="G21" s="47">
         <v>1250</v>
       </c>
-      <c r="H21" s="52">
+      <c r="H21" s="47">
         <v>0</v>
       </c>
-      <c r="I21" s="46" t="str">
+      <c r="I21" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="K21" s="90"/>
-      <c r="L21" s="82"/>
-      <c r="M21" s="90"/>
-      <c r="N21" s="90"/>
-      <c r="O21" s="90"/>
-      <c r="P21" s="90"/>
-      <c r="Q21" s="90"/>
-      <c r="R21" s="90"/>
-      <c r="S21" s="90"/>
-      <c r="T21" s="90"/>
-      <c r="U21" s="90"/>
+      <c r="K21" s="80"/>
+      <c r="L21" s="74"/>
+      <c r="M21" s="80"/>
+      <c r="N21" s="80"/>
+      <c r="O21" s="80"/>
+      <c r="P21" s="80"/>
+      <c r="Q21" s="80"/>
+      <c r="R21" s="80"/>
+      <c r="S21" s="80"/>
+      <c r="T21" s="80"/>
+      <c r="U21" s="80"/>
     </row>
     <row r="22" spans="3:21" ht="16" x14ac:dyDescent="0.35">
-      <c r="C22" s="48">
+      <c r="C22" s="43">
         <v>45856</v>
       </c>
-      <c r="D22" s="49" t="s">
+      <c r="D22" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="45">
         <v>90123456700</v>
       </c>
-      <c r="F22" s="54" t="s">
+      <c r="F22" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="G22" s="52">
+      <c r="G22" s="47">
         <v>350</v>
       </c>
-      <c r="H22" s="52">
+      <c r="H22" s="47">
         <v>0</v>
       </c>
-      <c r="I22" s="46" t="str">
+      <c r="I22" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="K22" s="90"/>
-      <c r="L22" s="82"/>
-      <c r="M22" s="90"/>
-      <c r="N22" s="90"/>
-      <c r="O22" s="90"/>
-      <c r="P22" s="90"/>
-      <c r="Q22" s="90"/>
-      <c r="R22" s="90"/>
-      <c r="S22" s="90"/>
-      <c r="T22" s="90"/>
-      <c r="U22" s="90"/>
+      <c r="K22" s="80"/>
+      <c r="L22" s="74"/>
+      <c r="M22" s="80"/>
+      <c r="N22" s="80"/>
+      <c r="O22" s="80"/>
+      <c r="P22" s="80"/>
+      <c r="Q22" s="80"/>
+      <c r="R22" s="80"/>
+      <c r="S22" s="80"/>
+      <c r="T22" s="80"/>
+      <c r="U22" s="80"/>
     </row>
     <row r="23" spans="3:21" ht="16" x14ac:dyDescent="0.35">
-      <c r="C23" s="48">
+      <c r="C23" s="43">
         <v>45891</v>
       </c>
-      <c r="D23" s="49" t="s">
+      <c r="D23" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="45">
         <v>11223344500</v>
       </c>
-      <c r="F23" s="54" t="s">
+      <c r="F23" s="49" t="s">
         <v>153</v>
       </c>
-      <c r="G23" s="52">
+      <c r="G23" s="47">
         <v>600</v>
       </c>
-      <c r="H23" s="52">
+      <c r="H23" s="47">
         <v>0</v>
       </c>
-      <c r="I23" s="46" t="str">
+      <c r="I23" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="K23" s="90"/>
-      <c r="L23" s="82"/>
-      <c r="M23" s="90"/>
-      <c r="N23" s="90"/>
-      <c r="O23" s="90"/>
-      <c r="P23" s="90"/>
-      <c r="Q23" s="90"/>
-      <c r="R23" s="90"/>
-      <c r="S23" s="90"/>
-      <c r="T23" s="90"/>
-      <c r="U23" s="90"/>
+      <c r="K23" s="80"/>
+      <c r="L23" s="74"/>
+      <c r="M23" s="80"/>
+      <c r="N23" s="80"/>
+      <c r="O23" s="80"/>
+      <c r="P23" s="80"/>
+      <c r="Q23" s="80"/>
+      <c r="R23" s="80"/>
+      <c r="S23" s="80"/>
+      <c r="T23" s="80"/>
+      <c r="U23" s="80"/>
     </row>
     <row r="24" spans="3:21" ht="16" x14ac:dyDescent="0.35">
-      <c r="C24" s="48"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="57"/>
-      <c r="I24" s="46" t="str">
+      <c r="C24" s="43"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="49"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K24" s="90"/>
-      <c r="L24" s="82"/>
-      <c r="M24" s="90"/>
-      <c r="N24" s="90"/>
-      <c r="O24" s="90"/>
-      <c r="P24" s="90"/>
-      <c r="Q24" s="90"/>
-      <c r="R24" s="90"/>
-      <c r="S24" s="90"/>
-      <c r="T24" s="90"/>
-      <c r="U24" s="90"/>
+      <c r="K24" s="80"/>
+      <c r="L24" s="74"/>
+      <c r="M24" s="80"/>
+      <c r="N24" s="80"/>
+      <c r="O24" s="80"/>
+      <c r="P24" s="80"/>
+      <c r="Q24" s="80"/>
+      <c r="R24" s="80"/>
+      <c r="S24" s="80"/>
+      <c r="T24" s="80"/>
+      <c r="U24" s="80"/>
     </row>
     <row r="25" spans="3:21" ht="16" x14ac:dyDescent="0.35">
-      <c r="C25" s="48"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="46" t="str">
+      <c r="C25" s="43"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K25" s="90"/>
-      <c r="L25" s="82"/>
-      <c r="M25" s="90"/>
-      <c r="N25" s="90"/>
-      <c r="O25" s="90"/>
-      <c r="P25" s="90"/>
-      <c r="Q25" s="90"/>
-      <c r="R25" s="90"/>
-      <c r="S25" s="90"/>
-      <c r="T25" s="90"/>
-      <c r="U25" s="90"/>
+      <c r="K25" s="80"/>
+      <c r="L25" s="74"/>
+      <c r="M25" s="80"/>
+      <c r="N25" s="80"/>
+      <c r="O25" s="80"/>
+      <c r="P25" s="80"/>
+      <c r="Q25" s="80"/>
+      <c r="R25" s="80"/>
+      <c r="S25" s="80"/>
+      <c r="T25" s="80"/>
+      <c r="U25" s="80"/>
     </row>
     <row r="26" spans="3:21" ht="16" x14ac:dyDescent="0.35">
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="46" t="str">
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="27" spans="3:21" ht="16" x14ac:dyDescent="0.35">
-      <c r="C27" s="51"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="55"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="46" t="str">
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="28" spans="3:21" ht="16" x14ac:dyDescent="0.35">
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="46" t="str">
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="49"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="29" spans="3:21" ht="16" x14ac:dyDescent="0.35">
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="55"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="46" t="str">
+      <c r="C29" s="46"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="30" spans="3:21" ht="16" x14ac:dyDescent="0.35">
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="54"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="46" t="str">
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="49"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="31" spans="3:21" ht="16" x14ac:dyDescent="0.35">
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="56"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="46" t="str">
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="32" spans="3:21" ht="16" x14ac:dyDescent="0.35">
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="55"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="46" t="str">
+      <c r="C32" s="46"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="49"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="33" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C33" s="51"/>
-      <c r="D33" s="51"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="46" t="str">
+      <c r="C33" s="46"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="34" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C34" s="51"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="55"/>
-      <c r="F34" s="54"/>
-      <c r="G34" s="56"/>
-      <c r="H34" s="57"/>
-      <c r="I34" s="46" t="str">
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="35" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="55"/>
-      <c r="F35" s="54"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="57"/>
-      <c r="I35" s="46" t="str">
+      <c r="C35" s="46"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="49"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="36" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="54"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="46" t="str">
+      <c r="C36" s="46"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="49"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="37" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C37" s="51"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="54"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="46" t="str">
+      <c r="C37" s="46"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="50"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="38" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C38" s="51"/>
-      <c r="D38" s="51"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="54"/>
-      <c r="G38" s="56"/>
-      <c r="H38" s="57"/>
-      <c r="I38" s="46" t="str">
+      <c r="C38" s="46"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="50"/>
+      <c r="F38" s="49"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="39" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="54"/>
-      <c r="G39" s="56"/>
-      <c r="H39" s="57"/>
-      <c r="I39" s="46" t="str">
+      <c r="C39" s="46"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="49"/>
+      <c r="G39" s="51"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="40" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C40" s="51"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="54"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="46" t="str">
+      <c r="C40" s="46"/>
+      <c r="D40" s="46"/>
+      <c r="E40" s="50"/>
+      <c r="F40" s="49"/>
+      <c r="G40" s="51"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="41" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C41" s="51"/>
-      <c r="D41" s="51"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="46" t="str">
+      <c r="C41" s="46"/>
+      <c r="D41" s="46"/>
+      <c r="E41" s="50"/>
+      <c r="F41" s="49"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="42" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C42" s="51"/>
-      <c r="D42" s="51"/>
-      <c r="E42" s="55"/>
-      <c r="F42" s="54"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="46" t="str">
+      <c r="C42" s="46"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="49"/>
+      <c r="G42" s="51"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="43" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C43" s="51"/>
-      <c r="D43" s="51"/>
-      <c r="E43" s="55"/>
-      <c r="F43" s="54"/>
-      <c r="G43" s="56"/>
-      <c r="H43" s="57"/>
-      <c r="I43" s="46" t="str">
+      <c r="C43" s="46"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="50"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="51"/>
+      <c r="H43" s="52"/>
+      <c r="I43" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="44" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C44" s="51"/>
-      <c r="D44" s="51"/>
-      <c r="E44" s="55"/>
-      <c r="F44" s="54"/>
-      <c r="G44" s="56"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="46" t="str">
+      <c r="C44" s="46"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="49"/>
+      <c r="G44" s="51"/>
+      <c r="H44" s="52"/>
+      <c r="I44" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="45" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C45" s="51"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="54"/>
-      <c r="G45" s="56"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="46" t="str">
+      <c r="C45" s="46"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="50"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="51"/>
+      <c r="H45" s="52"/>
+      <c r="I45" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="46" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C46" s="51"/>
-      <c r="D46" s="51"/>
-      <c r="E46" s="55"/>
-      <c r="F46" s="54"/>
-      <c r="G46" s="56"/>
-      <c r="H46" s="57"/>
-      <c r="I46" s="46" t="str">
+      <c r="C46" s="46"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="50"/>
+      <c r="F46" s="49"/>
+      <c r="G46" s="51"/>
+      <c r="H46" s="52"/>
+      <c r="I46" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="47" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C47" s="51"/>
-      <c r="D47" s="51"/>
-      <c r="E47" s="55"/>
-      <c r="F47" s="54"/>
-      <c r="G47" s="56"/>
-      <c r="H47" s="57"/>
-      <c r="I47" s="46" t="str">
+      <c r="C47" s="46"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="50"/>
+      <c r="F47" s="49"/>
+      <c r="G47" s="51"/>
+      <c r="H47" s="52"/>
+      <c r="I47" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="48" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C48" s="51"/>
-      <c r="D48" s="51"/>
-      <c r="E48" s="55"/>
-      <c r="F48" s="54"/>
-      <c r="G48" s="56"/>
-      <c r="H48" s="57"/>
-      <c r="I48" s="46" t="str">
+      <c r="C48" s="46"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="50"/>
+      <c r="F48" s="49"/>
+      <c r="G48" s="51"/>
+      <c r="H48" s="52"/>
+      <c r="I48" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C49" s="51"/>
-      <c r="D49" s="51"/>
-      <c r="E49" s="55"/>
-      <c r="F49" s="54"/>
-      <c r="G49" s="56"/>
-      <c r="H49" s="57"/>
-      <c r="I49" s="46" t="str">
+      <c r="C49" s="46"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="49"/>
+      <c r="G49" s="51"/>
+      <c r="H49" s="52"/>
+      <c r="I49" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="50" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C50" s="51"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="55"/>
-      <c r="F50" s="54"/>
-      <c r="G50" s="56"/>
-      <c r="H50" s="57"/>
-      <c r="I50" s="46" t="str">
+      <c r="C50" s="46"/>
+      <c r="D50" s="46"/>
+      <c r="E50" s="50"/>
+      <c r="F50" s="49"/>
+      <c r="G50" s="51"/>
+      <c r="H50" s="52"/>
+      <c r="I50" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="51" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C51" s="51"/>
-      <c r="D51" s="51"/>
-      <c r="E51" s="53"/>
-      <c r="F51" s="54"/>
-      <c r="G51" s="56"/>
-      <c r="H51" s="57"/>
-      <c r="I51" s="59"/>
+      <c r="C51" s="46"/>
+      <c r="D51" s="46"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="49"/>
+      <c r="G51" s="51"/>
+      <c r="H51" s="52"/>
+      <c r="I51" s="54"/>
     </row>
     <row r="52" spans="3:9" x14ac:dyDescent="0.35"/>
     <row r="53" spans="3:9" x14ac:dyDescent="0.35"/>
     <row r="54" spans="3:9" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <sheetProtection sheet="1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="C12:I12"/>
   </mergeCells>
@@ -26826,15 +26781,11 @@
       <formula>NOT(ISERROR(SEARCH("CONCLUÍDO",I14)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
+  <dataValidations count="4">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H14:H51" xr:uid="{3D0F9760-8E86-4C46-A2E6-2BFF9079DFE1}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{ED649657-6B17-4D6D-A2B5-2A51D5D6FA4E}">
-      <formula1>43831</formula1>
-      <formula2>49674</formula2>
-    </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Essa faixa é apenas uma validação inicial. Depois podemos ajustá-la para aceitar somente datas do ano-calendário correspondente." sqref="C15:C23" xr:uid="{C65B1BED-6AD0-4AD7-9C9B-FF1749A25D28}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14:C51" xr:uid="{ED649657-6B17-4D6D-A2B5-2A51D5D6FA4E}">
       <formula1>43831</formula1>
       <formula2>49674</formula2>
     </dataValidation>
@@ -26861,941 +26812,941 @@
   <dimension ref="A1:T54"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.90625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="22.81640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="13.7265625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="13.453125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="13" style="5" customWidth="1"/>
-    <col min="8" max="8" width="13.08984375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="15" style="5" customWidth="1"/>
-    <col min="10" max="10" width="7.54296875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="8.7265625" style="5" hidden="1"/>
-    <col min="12" max="12" width="11.36328125" style="35" hidden="1"/>
-    <col min="13" max="16384" width="8.7265625" style="5" hidden="1"/>
+    <col min="1" max="1" width="29.90625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.7265625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="22.81640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="13" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.08984375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="15" style="3" customWidth="1"/>
+    <col min="10" max="10" width="7.54296875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="8.7265625" style="3" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.36328125" style="31" hidden="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.7265625" style="3" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:20" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="J3" s="58">
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="J3" s="53">
         <f>SUM(G:G)</f>
         <v>250500</v>
       </c>
-      <c r="L3" s="89"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="90"/>
-      <c r="O3" s="90"/>
-      <c r="P3" s="90"/>
-      <c r="Q3" s="90"/>
-      <c r="R3" s="90"/>
-      <c r="S3" s="90"/>
-      <c r="T3" s="90"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="80"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="J4" s="58">
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="J4" s="53">
         <f>SUM(H:H)</f>
         <v>249500</v>
       </c>
-      <c r="L4" s="89"/>
-      <c r="M4" s="90"/>
-      <c r="N4" s="90"/>
-      <c r="O4" s="90"/>
-      <c r="P4" s="90"/>
-      <c r="Q4" s="90"/>
-      <c r="R4" s="90"/>
-      <c r="S4" s="90"/>
-      <c r="T4" s="90"/>
+      <c r="L4" s="79"/>
+      <c r="M4" s="80"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="80"/>
+      <c r="R4" s="80"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="80"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="J5" s="39">
+      <c r="J5" s="35">
         <f>COUNTIF(I:I,"PENDENTE")+COUNTIF(I:I,"INCOMPLETO")</f>
         <v>1</v>
       </c>
-      <c r="L5" s="82"/>
-      <c r="M5" s="90"/>
-      <c r="N5" s="90"/>
-      <c r="O5" s="90"/>
-      <c r="P5" s="90"/>
-      <c r="Q5" s="90"/>
-      <c r="R5" s="90"/>
-      <c r="S5" s="90"/>
-      <c r="T5" s="90"/>
+      <c r="L5" s="74"/>
+      <c r="M5" s="80"/>
+      <c r="N5" s="80"/>
+      <c r="O5" s="80"/>
+      <c r="P5" s="80"/>
+      <c r="Q5" s="80"/>
+      <c r="R5" s="80"/>
+      <c r="S5" s="80"/>
+      <c r="T5" s="80"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="L6" s="82"/>
-      <c r="M6" s="90"/>
-      <c r="N6" s="90"/>
-      <c r="O6" s="90"/>
-      <c r="P6" s="90"/>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90"/>
-      <c r="T6" s="90"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="80"/>
+      <c r="O6" s="80"/>
+      <c r="P6" s="80"/>
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80"/>
+      <c r="T6" s="80"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="L7" s="82"/>
-      <c r="M7" s="90"/>
-      <c r="N7" s="90"/>
-      <c r="O7" s="90"/>
-      <c r="P7" s="90"/>
-      <c r="Q7" s="90"/>
-      <c r="R7" s="90"/>
-      <c r="S7" s="90"/>
-      <c r="T7" s="90"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="80"/>
+      <c r="N7" s="80"/>
+      <c r="O7" s="80"/>
+      <c r="P7" s="80"/>
+      <c r="Q7" s="80"/>
+      <c r="R7" s="80"/>
+      <c r="S7" s="80"/>
+      <c r="T7" s="80"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="L8" s="82"/>
-      <c r="M8" s="90"/>
-      <c r="N8" s="90"/>
-      <c r="O8" s="90"/>
-      <c r="P8" s="90"/>
-      <c r="Q8" s="90"/>
-      <c r="R8" s="90"/>
-      <c r="S8" s="90"/>
-      <c r="T8" s="90"/>
+      <c r="L8" s="74"/>
+      <c r="M8" s="80"/>
+      <c r="N8" s="80"/>
+      <c r="O8" s="80"/>
+      <c r="P8" s="80"/>
+      <c r="Q8" s="80"/>
+      <c r="R8" s="80"/>
+      <c r="S8" s="80"/>
+      <c r="T8" s="80"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="L9" s="82"/>
-      <c r="M9" s="90"/>
-      <c r="N9" s="90"/>
-      <c r="O9" s="90"/>
-      <c r="P9" s="90"/>
-      <c r="Q9" s="90"/>
-      <c r="R9" s="90"/>
-      <c r="S9" s="90"/>
-      <c r="T9" s="90"/>
+      <c r="L9" s="74"/>
+      <c r="M9" s="80"/>
+      <c r="N9" s="80"/>
+      <c r="O9" s="80"/>
+      <c r="P9" s="80"/>
+      <c r="Q9" s="80"/>
+      <c r="R9" s="80"/>
+      <c r="S9" s="80"/>
+      <c r="T9" s="80"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="L10" s="82"/>
-      <c r="M10" s="90"/>
-      <c r="N10" s="90"/>
-      <c r="O10" s="90"/>
-      <c r="P10" s="90"/>
-      <c r="Q10" s="90"/>
-      <c r="R10" s="90"/>
-      <c r="S10" s="90"/>
-      <c r="T10" s="90"/>
+      <c r="L10" s="74"/>
+      <c r="M10" s="80"/>
+      <c r="N10" s="80"/>
+      <c r="O10" s="80"/>
+      <c r="P10" s="80"/>
+      <c r="Q10" s="80"/>
+      <c r="R10" s="80"/>
+      <c r="S10" s="80"/>
+      <c r="T10" s="80"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="L11" s="82"/>
-      <c r="M11" s="90"/>
-      <c r="N11" s="90"/>
-      <c r="O11" s="90"/>
-      <c r="P11" s="90"/>
-      <c r="Q11" s="90"/>
-      <c r="R11" s="90"/>
-      <c r="S11" s="90"/>
-      <c r="T11" s="90"/>
-    </row>
-    <row r="12" spans="1:20" s="42" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="41"/>
-      <c r="C12" s="43" t="s">
+      <c r="L11" s="74"/>
+      <c r="M11" s="80"/>
+      <c r="N11" s="80"/>
+      <c r="O11" s="80"/>
+      <c r="P11" s="80"/>
+      <c r="Q11" s="80"/>
+      <c r="R11" s="80"/>
+      <c r="S11" s="80"/>
+      <c r="T11" s="80"/>
+    </row>
+    <row r="12" spans="1:20" s="38" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="37"/>
+      <c r="C12" s="84" t="s">
         <v>161</v>
       </c>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="L12" s="91"/>
-      <c r="M12" s="92"/>
-      <c r="N12" s="92"/>
-      <c r="O12" s="92"/>
-      <c r="P12" s="92"/>
-      <c r="Q12" s="92"/>
-      <c r="R12" s="92"/>
-      <c r="S12" s="92"/>
-      <c r="T12" s="92"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
+      <c r="L12" s="81"/>
+      <c r="M12" s="82"/>
+      <c r="N12" s="82"/>
+      <c r="O12" s="82"/>
+      <c r="P12" s="82"/>
+      <c r="Q12" s="82"/>
+      <c r="R12" s="82"/>
+      <c r="S12" s="82"/>
+      <c r="T12" s="82"/>
     </row>
     <row r="13" spans="1:20" ht="26" x14ac:dyDescent="0.35">
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="D13" s="45" t="s">
+      <c r="D13" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="E13" s="45" t="s">
+      <c r="E13" s="40" t="s">
         <v>156</v>
       </c>
-      <c r="F13" s="45" t="s">
+      <c r="F13" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="G13" s="45" t="s">
+      <c r="G13" s="40" t="s">
         <v>158</v>
       </c>
-      <c r="H13" s="45" t="s">
+      <c r="H13" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I13" s="45" t="s">
+      <c r="I13" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="L13" s="82"/>
-      <c r="M13" s="90"/>
-      <c r="N13" s="90"/>
-      <c r="O13" s="90"/>
-      <c r="P13" s="90"/>
-      <c r="Q13" s="90"/>
-      <c r="R13" s="90"/>
-      <c r="S13" s="90"/>
-      <c r="T13" s="90"/>
+      <c r="L13" s="74"/>
+      <c r="M13" s="80"/>
+      <c r="N13" s="80"/>
+      <c r="O13" s="80"/>
+      <c r="P13" s="80"/>
+      <c r="Q13" s="80"/>
+      <c r="R13" s="80"/>
+      <c r="S13" s="80"/>
+      <c r="T13" s="80"/>
     </row>
     <row r="14" spans="1:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C14" s="48" t="s">
+      <c r="C14" s="43" t="s">
         <v>162</v>
       </c>
-      <c r="D14" s="49" t="s">
+      <c r="D14" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="E14" s="50" t="s">
+      <c r="E14" s="45" t="s">
         <v>164</v>
       </c>
-      <c r="F14" s="61">
+      <c r="F14" s="56">
         <v>43539</v>
       </c>
-      <c r="G14" s="52">
+      <c r="G14" s="47">
         <v>180000</v>
       </c>
-      <c r="H14" s="52">
+      <c r="H14" s="47">
         <v>180000</v>
       </c>
-      <c r="I14" s="46" t="str">
+      <c r="I14" s="41" t="str">
         <f t="shared" ref="I14:I50" si="0">IF(COUNTA(C14:H14)=0,"",IF(OR(C14="",D14="",E14="",F14="",G14="",H14=""),"INCOMPLETO","CONCLUÍDO"))</f>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="L14" s="82"/>
-      <c r="M14" s="90"/>
-      <c r="N14" s="90"/>
-      <c r="O14" s="90"/>
-      <c r="P14" s="90"/>
-      <c r="Q14" s="90"/>
-      <c r="R14" s="90"/>
-      <c r="S14" s="90"/>
-      <c r="T14" s="90"/>
+      <c r="L14" s="74"/>
+      <c r="M14" s="80"/>
+      <c r="N14" s="80"/>
+      <c r="O14" s="80"/>
+      <c r="P14" s="80"/>
+      <c r="Q14" s="80"/>
+      <c r="R14" s="80"/>
+      <c r="S14" s="80"/>
+      <c r="T14" s="80"/>
     </row>
     <row r="15" spans="1:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C15" s="48" t="s">
+      <c r="C15" s="43" t="s">
         <v>165</v>
       </c>
-      <c r="D15" s="49" t="s">
+      <c r="D15" s="44" t="s">
         <v>166</v>
       </c>
-      <c r="E15" s="50" t="s">
+      <c r="E15" s="45" t="s">
         <v>164</v>
       </c>
-      <c r="F15" s="61">
+      <c r="F15" s="56">
         <v>44722</v>
       </c>
-      <c r="G15" s="52">
+      <c r="G15" s="47">
         <v>45000</v>
       </c>
-      <c r="H15" s="52">
+      <c r="H15" s="47">
         <v>45000</v>
       </c>
-      <c r="I15" s="46" t="str">
+      <c r="I15" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="L15" s="82"/>
-      <c r="M15" s="90"/>
-      <c r="N15" s="90"/>
-      <c r="O15" s="90"/>
-      <c r="P15" s="90"/>
-      <c r="Q15" s="90"/>
-      <c r="R15" s="90"/>
-      <c r="S15" s="90"/>
-      <c r="T15" s="90"/>
+      <c r="L15" s="74"/>
+      <c r="M15" s="80"/>
+      <c r="N15" s="80"/>
+      <c r="O15" s="80"/>
+      <c r="P15" s="80"/>
+      <c r="Q15" s="80"/>
+      <c r="R15" s="80"/>
+      <c r="S15" s="80"/>
+      <c r="T15" s="80"/>
     </row>
     <row r="16" spans="1:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C16" s="48" t="s">
+      <c r="C16" s="43" t="s">
         <v>167</v>
       </c>
-      <c r="D16" s="49" t="s">
+      <c r="D16" s="44" t="s">
         <v>168</v>
       </c>
-      <c r="E16" s="50" t="s">
+      <c r="E16" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="F16" s="61">
+      <c r="F16" s="56">
         <v>44938</v>
       </c>
-      <c r="G16" s="52">
+      <c r="G16" s="47">
         <v>12000</v>
       </c>
-      <c r="H16" s="52">
+      <c r="H16" s="47">
         <v>14500</v>
       </c>
-      <c r="I16" s="46" t="str">
+      <c r="I16" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="L16" s="82"/>
-      <c r="M16" s="90"/>
-      <c r="N16" s="90"/>
-      <c r="O16" s="90"/>
-      <c r="P16" s="90"/>
-      <c r="Q16" s="90"/>
-      <c r="R16" s="90"/>
-      <c r="S16" s="90"/>
-      <c r="T16" s="90"/>
+      <c r="L16" s="74"/>
+      <c r="M16" s="80"/>
+      <c r="N16" s="80"/>
+      <c r="O16" s="80"/>
+      <c r="P16" s="80"/>
+      <c r="Q16" s="80"/>
+      <c r="R16" s="80"/>
+      <c r="S16" s="80"/>
+      <c r="T16" s="80"/>
     </row>
     <row r="17" spans="3:20" ht="32" x14ac:dyDescent="0.35">
-      <c r="C17" s="48" t="s">
+      <c r="C17" s="43" t="s">
         <v>169</v>
       </c>
-      <c r="D17" s="49" t="s">
+      <c r="D17" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="E17" s="50" t="s">
+      <c r="E17" s="45" t="s">
         <v>164</v>
       </c>
-      <c r="F17" s="61">
+      <c r="F17" s="56">
         <v>44428</v>
       </c>
-      <c r="G17" s="52">
+      <c r="G17" s="47">
         <v>10000</v>
       </c>
-      <c r="H17" s="52">
+      <c r="H17" s="47">
         <v>10000</v>
       </c>
-      <c r="I17" s="46" t="str">
+      <c r="I17" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
-      <c r="L17" s="82"/>
-      <c r="M17" s="90"/>
-      <c r="N17" s="90"/>
-      <c r="O17" s="90"/>
-      <c r="P17" s="90"/>
-      <c r="Q17" s="90"/>
-      <c r="R17" s="90"/>
-      <c r="S17" s="90"/>
-      <c r="T17" s="90"/>
+      <c r="L17" s="74"/>
+      <c r="M17" s="80"/>
+      <c r="N17" s="80"/>
+      <c r="O17" s="80"/>
+      <c r="P17" s="80"/>
+      <c r="Q17" s="80"/>
+      <c r="R17" s="80"/>
+      <c r="S17" s="80"/>
+      <c r="T17" s="80"/>
     </row>
     <row r="18" spans="3:20" ht="32" x14ac:dyDescent="0.35">
-      <c r="C18" s="48" t="s">
+      <c r="C18" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="49" t="s">
+      <c r="D18" s="44" t="s">
         <v>172</v>
       </c>
-      <c r="E18" s="50" t="s">
+      <c r="E18" s="45" t="s">
         <v>164</v>
       </c>
-      <c r="F18" s="61">
+      <c r="F18" s="56">
         <v>45400</v>
       </c>
-      <c r="G18" s="52">
+      <c r="G18" s="47">
         <v>3500</v>
       </c>
-      <c r="H18" s="52"/>
-      <c r="I18" s="46" t="str">
+      <c r="H18" s="47"/>
+      <c r="I18" s="41" t="str">
         <f t="shared" si="0"/>
         <v>INCOMPLETO</v>
       </c>
-      <c r="L18" s="82"/>
-      <c r="M18" s="90"/>
-      <c r="N18" s="90"/>
-      <c r="O18" s="90"/>
-      <c r="P18" s="90"/>
-      <c r="Q18" s="90"/>
-      <c r="R18" s="90"/>
-      <c r="S18" s="90"/>
-      <c r="T18" s="90"/>
+      <c r="L18" s="74"/>
+      <c r="M18" s="80"/>
+      <c r="N18" s="80"/>
+      <c r="O18" s="80"/>
+      <c r="P18" s="80"/>
+      <c r="Q18" s="80"/>
+      <c r="R18" s="80"/>
+      <c r="S18" s="80"/>
+      <c r="T18" s="80"/>
     </row>
     <row r="19" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C19" s="48"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="46" t="str">
+      <c r="C19" s="43"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L19" s="82"/>
-      <c r="M19" s="90"/>
-      <c r="N19" s="90"/>
-      <c r="O19" s="90"/>
-      <c r="P19" s="90"/>
-      <c r="Q19" s="90"/>
-      <c r="R19" s="90"/>
-      <c r="S19" s="90"/>
-      <c r="T19" s="90"/>
+      <c r="L19" s="74"/>
+      <c r="M19" s="80"/>
+      <c r="N19" s="80"/>
+      <c r="O19" s="80"/>
+      <c r="P19" s="80"/>
+      <c r="Q19" s="80"/>
+      <c r="R19" s="80"/>
+      <c r="S19" s="80"/>
+      <c r="T19" s="80"/>
     </row>
     <row r="20" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C20" s="48"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="46" t="str">
+      <c r="C20" s="43"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L20" s="82"/>
-      <c r="M20" s="90"/>
-      <c r="N20" s="90"/>
-      <c r="O20" s="90"/>
-      <c r="P20" s="90"/>
-      <c r="Q20" s="90"/>
-      <c r="R20" s="90"/>
-      <c r="S20" s="90"/>
-      <c r="T20" s="90"/>
+      <c r="L20" s="74"/>
+      <c r="M20" s="80"/>
+      <c r="N20" s="80"/>
+      <c r="O20" s="80"/>
+      <c r="P20" s="80"/>
+      <c r="Q20" s="80"/>
+      <c r="R20" s="80"/>
+      <c r="S20" s="80"/>
+      <c r="T20" s="80"/>
     </row>
     <row r="21" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C21" s="48"/>
-      <c r="D21" s="49"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="61"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="46" t="str">
+      <c r="C21" s="43"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L21" s="82"/>
-      <c r="M21" s="90"/>
-      <c r="N21" s="90"/>
-      <c r="O21" s="90"/>
-      <c r="P21" s="90"/>
-      <c r="Q21" s="90"/>
-      <c r="R21" s="90"/>
-      <c r="S21" s="90"/>
-      <c r="T21" s="90"/>
+      <c r="L21" s="74"/>
+      <c r="M21" s="80"/>
+      <c r="N21" s="80"/>
+      <c r="O21" s="80"/>
+      <c r="P21" s="80"/>
+      <c r="Q21" s="80"/>
+      <c r="R21" s="80"/>
+      <c r="S21" s="80"/>
+      <c r="T21" s="80"/>
     </row>
     <row r="22" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C22" s="48"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="46" t="str">
+      <c r="C22" s="43"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L22" s="82"/>
-      <c r="M22" s="90"/>
-      <c r="N22" s="90"/>
-      <c r="O22" s="90"/>
-      <c r="P22" s="90"/>
-      <c r="Q22" s="90"/>
-      <c r="R22" s="90"/>
-      <c r="S22" s="90"/>
-      <c r="T22" s="90"/>
+      <c r="L22" s="74"/>
+      <c r="M22" s="80"/>
+      <c r="N22" s="80"/>
+      <c r="O22" s="80"/>
+      <c r="P22" s="80"/>
+      <c r="Q22" s="80"/>
+      <c r="R22" s="80"/>
+      <c r="S22" s="80"/>
+      <c r="T22" s="80"/>
     </row>
     <row r="23" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C23" s="48"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="61"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="46" t="str">
+      <c r="C23" s="43"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L23" s="82"/>
-      <c r="M23" s="90"/>
-      <c r="N23" s="90"/>
-      <c r="O23" s="90"/>
-      <c r="P23" s="90"/>
-      <c r="Q23" s="90"/>
-      <c r="R23" s="90"/>
-      <c r="S23" s="90"/>
-      <c r="T23" s="90"/>
+      <c r="L23" s="74"/>
+      <c r="M23" s="80"/>
+      <c r="N23" s="80"/>
+      <c r="O23" s="80"/>
+      <c r="P23" s="80"/>
+      <c r="Q23" s="80"/>
+      <c r="R23" s="80"/>
+      <c r="S23" s="80"/>
+      <c r="T23" s="80"/>
     </row>
     <row r="24" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C24" s="48"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="61"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="46" t="str">
+      <c r="C24" s="43"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L24" s="82"/>
-      <c r="M24" s="90"/>
-      <c r="N24" s="90"/>
-      <c r="O24" s="90"/>
-      <c r="P24" s="90"/>
-      <c r="Q24" s="90"/>
-      <c r="R24" s="90"/>
-      <c r="S24" s="90"/>
-      <c r="T24" s="90"/>
+      <c r="L24" s="74"/>
+      <c r="M24" s="80"/>
+      <c r="N24" s="80"/>
+      <c r="O24" s="80"/>
+      <c r="P24" s="80"/>
+      <c r="Q24" s="80"/>
+      <c r="R24" s="80"/>
+      <c r="S24" s="80"/>
+      <c r="T24" s="80"/>
     </row>
     <row r="25" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C25" s="48"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="61"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="46" t="str">
+      <c r="C25" s="43"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L25" s="82"/>
-      <c r="M25" s="90"/>
-      <c r="N25" s="90"/>
-      <c r="O25" s="90"/>
-      <c r="P25" s="90"/>
-      <c r="Q25" s="90"/>
-      <c r="R25" s="90"/>
-      <c r="S25" s="90"/>
-      <c r="T25" s="90"/>
+      <c r="L25" s="74"/>
+      <c r="M25" s="80"/>
+      <c r="N25" s="80"/>
+      <c r="O25" s="80"/>
+      <c r="P25" s="80"/>
+      <c r="Q25" s="80"/>
+      <c r="R25" s="80"/>
+      <c r="S25" s="80"/>
+      <c r="T25" s="80"/>
     </row>
     <row r="26" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C26" s="51"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="61"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="46" t="str">
+      <c r="C26" s="46"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L26" s="82"/>
-      <c r="M26" s="90"/>
-      <c r="N26" s="90"/>
-      <c r="O26" s="90"/>
-      <c r="P26" s="90"/>
-      <c r="Q26" s="90"/>
-      <c r="R26" s="90"/>
-      <c r="S26" s="90"/>
-      <c r="T26" s="90"/>
+      <c r="L26" s="74"/>
+      <c r="M26" s="80"/>
+      <c r="N26" s="80"/>
+      <c r="O26" s="80"/>
+      <c r="P26" s="80"/>
+      <c r="Q26" s="80"/>
+      <c r="R26" s="80"/>
+      <c r="S26" s="80"/>
+      <c r="T26" s="80"/>
     </row>
     <row r="27" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C27" s="51"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="61"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="46" t="str">
+      <c r="C27" s="46"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L27" s="82"/>
-      <c r="M27" s="90"/>
-      <c r="N27" s="90"/>
-      <c r="O27" s="90"/>
-      <c r="P27" s="90"/>
-      <c r="Q27" s="90"/>
-      <c r="R27" s="90"/>
-      <c r="S27" s="90"/>
-      <c r="T27" s="90"/>
+      <c r="L27" s="74"/>
+      <c r="M27" s="80"/>
+      <c r="N27" s="80"/>
+      <c r="O27" s="80"/>
+      <c r="P27" s="80"/>
+      <c r="Q27" s="80"/>
+      <c r="R27" s="80"/>
+      <c r="S27" s="80"/>
+      <c r="T27" s="80"/>
     </row>
     <row r="28" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C28" s="51"/>
-      <c r="D28" s="49"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="61"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="46" t="str">
+      <c r="C28" s="46"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L28" s="82"/>
-      <c r="M28" s="90"/>
-      <c r="N28" s="90"/>
-      <c r="O28" s="90"/>
-      <c r="P28" s="90"/>
-      <c r="Q28" s="90"/>
-      <c r="R28" s="90"/>
-      <c r="S28" s="90"/>
-      <c r="T28" s="90"/>
+      <c r="L28" s="74"/>
+      <c r="M28" s="80"/>
+      <c r="N28" s="80"/>
+      <c r="O28" s="80"/>
+      <c r="P28" s="80"/>
+      <c r="Q28" s="80"/>
+      <c r="R28" s="80"/>
+      <c r="S28" s="80"/>
+      <c r="T28" s="80"/>
     </row>
     <row r="29" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C29" s="51"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="61"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="46" t="str">
+      <c r="C29" s="46"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="47"/>
+      <c r="I29" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L29" s="82"/>
-      <c r="M29" s="90"/>
-      <c r="N29" s="90"/>
-      <c r="O29" s="90"/>
-      <c r="P29" s="90"/>
-      <c r="Q29" s="90"/>
-      <c r="R29" s="90"/>
-      <c r="S29" s="90"/>
-      <c r="T29" s="90"/>
+      <c r="L29" s="74"/>
+      <c r="M29" s="80"/>
+      <c r="N29" s="80"/>
+      <c r="O29" s="80"/>
+      <c r="P29" s="80"/>
+      <c r="Q29" s="80"/>
+      <c r="R29" s="80"/>
+      <c r="S29" s="80"/>
+      <c r="T29" s="80"/>
     </row>
     <row r="30" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C30" s="51"/>
-      <c r="D30" s="49"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="46" t="str">
+      <c r="C30" s="46"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="47"/>
+      <c r="I30" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L30" s="82"/>
-      <c r="M30" s="90"/>
-      <c r="N30" s="90"/>
-      <c r="O30" s="90"/>
-      <c r="P30" s="90"/>
-      <c r="Q30" s="90"/>
-      <c r="R30" s="90"/>
-      <c r="S30" s="90"/>
-      <c r="T30" s="90"/>
+      <c r="L30" s="74"/>
+      <c r="M30" s="80"/>
+      <c r="N30" s="80"/>
+      <c r="O30" s="80"/>
+      <c r="P30" s="80"/>
+      <c r="Q30" s="80"/>
+      <c r="R30" s="80"/>
+      <c r="S30" s="80"/>
+      <c r="T30" s="80"/>
     </row>
     <row r="31" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C31" s="51"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="46" t="str">
+      <c r="C31" s="46"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="56"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L31" s="82"/>
-      <c r="M31" s="90"/>
-      <c r="N31" s="90"/>
-      <c r="O31" s="90"/>
-      <c r="P31" s="90"/>
-      <c r="Q31" s="90"/>
-      <c r="R31" s="90"/>
-      <c r="S31" s="90"/>
-      <c r="T31" s="90"/>
+      <c r="L31" s="74"/>
+      <c r="M31" s="80"/>
+      <c r="N31" s="80"/>
+      <c r="O31" s="80"/>
+      <c r="P31" s="80"/>
+      <c r="Q31" s="80"/>
+      <c r="R31" s="80"/>
+      <c r="S31" s="80"/>
+      <c r="T31" s="80"/>
     </row>
     <row r="32" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C32" s="51"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="46" t="str">
+      <c r="C32" s="46"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="56"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L32" s="82"/>
-      <c r="M32" s="90"/>
-      <c r="N32" s="90"/>
-      <c r="O32" s="90"/>
-      <c r="P32" s="90"/>
-      <c r="Q32" s="90"/>
-      <c r="R32" s="90"/>
-      <c r="S32" s="90"/>
-      <c r="T32" s="90"/>
+      <c r="L32" s="74"/>
+      <c r="M32" s="80"/>
+      <c r="N32" s="80"/>
+      <c r="O32" s="80"/>
+      <c r="P32" s="80"/>
+      <c r="Q32" s="80"/>
+      <c r="R32" s="80"/>
+      <c r="S32" s="80"/>
+      <c r="T32" s="80"/>
     </row>
     <row r="33" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C33" s="51"/>
-      <c r="D33" s="49"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="61"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="46" t="str">
+      <c r="C33" s="46"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="47"/>
+      <c r="I33" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L33" s="82"/>
-      <c r="M33" s="90"/>
-      <c r="N33" s="90"/>
-      <c r="O33" s="90"/>
-      <c r="P33" s="90"/>
-      <c r="Q33" s="90"/>
-      <c r="R33" s="90"/>
-      <c r="S33" s="90"/>
-      <c r="T33" s="90"/>
+      <c r="L33" s="74"/>
+      <c r="M33" s="80"/>
+      <c r="N33" s="80"/>
+      <c r="O33" s="80"/>
+      <c r="P33" s="80"/>
+      <c r="Q33" s="80"/>
+      <c r="R33" s="80"/>
+      <c r="S33" s="80"/>
+      <c r="T33" s="80"/>
     </row>
     <row r="34" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C34" s="51"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="61"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="46" t="str">
+      <c r="C34" s="46"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="56"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="47"/>
+      <c r="I34" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L34" s="82"/>
-      <c r="M34" s="90"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="90"/>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="90"/>
-      <c r="S34" s="90"/>
-      <c r="T34" s="90"/>
+      <c r="L34" s="74"/>
+      <c r="M34" s="80"/>
+      <c r="N34" s="80"/>
+      <c r="O34" s="80"/>
+      <c r="P34" s="80"/>
+      <c r="Q34" s="80"/>
+      <c r="R34" s="80"/>
+      <c r="S34" s="80"/>
+      <c r="T34" s="80"/>
     </row>
     <row r="35" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C35" s="51"/>
-      <c r="D35" s="49"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="61"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="46" t="str">
+      <c r="C35" s="46"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L35" s="82"/>
-      <c r="M35" s="90"/>
-      <c r="N35" s="90"/>
-      <c r="O35" s="90"/>
-      <c r="P35" s="90"/>
-      <c r="Q35" s="90"/>
-      <c r="R35" s="90"/>
-      <c r="S35" s="90"/>
-      <c r="T35" s="90"/>
+      <c r="L35" s="74"/>
+      <c r="M35" s="80"/>
+      <c r="N35" s="80"/>
+      <c r="O35" s="80"/>
+      <c r="P35" s="80"/>
+      <c r="Q35" s="80"/>
+      <c r="R35" s="80"/>
+      <c r="S35" s="80"/>
+      <c r="T35" s="80"/>
     </row>
     <row r="36" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C36" s="51"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="61"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="52"/>
-      <c r="I36" s="46" t="str">
+      <c r="C36" s="46"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="56"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L36" s="82"/>
-      <c r="M36" s="90"/>
-      <c r="N36" s="90"/>
-      <c r="O36" s="90"/>
-      <c r="P36" s="90"/>
-      <c r="Q36" s="90"/>
-      <c r="R36" s="90"/>
-      <c r="S36" s="90"/>
-      <c r="T36" s="90"/>
+      <c r="L36" s="74"/>
+      <c r="M36" s="80"/>
+      <c r="N36" s="80"/>
+      <c r="O36" s="80"/>
+      <c r="P36" s="80"/>
+      <c r="Q36" s="80"/>
+      <c r="R36" s="80"/>
+      <c r="S36" s="80"/>
+      <c r="T36" s="80"/>
     </row>
     <row r="37" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C37" s="51"/>
-      <c r="D37" s="49"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="61"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="52"/>
-      <c r="I37" s="46" t="str">
+      <c r="C37" s="46"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="56"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="47"/>
+      <c r="I37" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L37" s="82"/>
-      <c r="M37" s="90"/>
-      <c r="N37" s="90"/>
-      <c r="O37" s="90"/>
-      <c r="P37" s="90"/>
-      <c r="Q37" s="90"/>
-      <c r="R37" s="90"/>
-      <c r="S37" s="90"/>
-      <c r="T37" s="90"/>
+      <c r="L37" s="74"/>
+      <c r="M37" s="80"/>
+      <c r="N37" s="80"/>
+      <c r="O37" s="80"/>
+      <c r="P37" s="80"/>
+      <c r="Q37" s="80"/>
+      <c r="R37" s="80"/>
+      <c r="S37" s="80"/>
+      <c r="T37" s="80"/>
     </row>
     <row r="38" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C38" s="51"/>
-      <c r="D38" s="49"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="51"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="46" t="str">
+      <c r="C38" s="46"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="47"/>
+      <c r="I38" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L38" s="82"/>
-      <c r="M38" s="90"/>
-      <c r="N38" s="90"/>
-      <c r="O38" s="90"/>
-      <c r="P38" s="90"/>
-      <c r="Q38" s="90"/>
-      <c r="R38" s="90"/>
-      <c r="S38" s="90"/>
-      <c r="T38" s="90"/>
+      <c r="L38" s="74"/>
+      <c r="M38" s="80"/>
+      <c r="N38" s="80"/>
+      <c r="O38" s="80"/>
+      <c r="P38" s="80"/>
+      <c r="Q38" s="80"/>
+      <c r="R38" s="80"/>
+      <c r="S38" s="80"/>
+      <c r="T38" s="80"/>
     </row>
     <row r="39" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C39" s="51"/>
-      <c r="D39" s="49"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="52"/>
-      <c r="I39" s="46" t="str">
+      <c r="C39" s="46"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="46"/>
+      <c r="H39" s="47"/>
+      <c r="I39" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="40" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C40" s="51"/>
-      <c r="D40" s="49"/>
-      <c r="E40" s="50"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="51"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="46" t="str">
+      <c r="C40" s="46"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="46"/>
+      <c r="H40" s="47"/>
+      <c r="I40" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="41" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C41" s="51"/>
-      <c r="D41" s="49"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="51"/>
-      <c r="H41" s="52"/>
-      <c r="I41" s="46" t="str">
+      <c r="C41" s="46"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="56"/>
+      <c r="G41" s="46"/>
+      <c r="H41" s="47"/>
+      <c r="I41" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="42" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C42" s="51"/>
-      <c r="D42" s="49"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="51"/>
-      <c r="H42" s="52"/>
-      <c r="I42" s="46" t="str">
+      <c r="C42" s="46"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="46"/>
+      <c r="H42" s="47"/>
+      <c r="I42" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="43" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C43" s="51"/>
-      <c r="D43" s="49"/>
-      <c r="E43" s="50"/>
-      <c r="F43" s="61"/>
-      <c r="G43" s="51"/>
-      <c r="H43" s="52"/>
-      <c r="I43" s="46" t="str">
+      <c r="C43" s="46"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="46"/>
+      <c r="H43" s="47"/>
+      <c r="I43" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="44" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C44" s="51"/>
-      <c r="D44" s="49"/>
-      <c r="E44" s="50"/>
-      <c r="F44" s="61"/>
-      <c r="G44" s="51"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="46" t="str">
+      <c r="C44" s="46"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="45"/>
+      <c r="F44" s="56"/>
+      <c r="G44" s="46"/>
+      <c r="H44" s="47"/>
+      <c r="I44" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="45" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C45" s="51"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="50"/>
-      <c r="F45" s="61"/>
-      <c r="G45" s="51"/>
-      <c r="H45" s="52"/>
-      <c r="I45" s="46" t="str">
+      <c r="C45" s="46"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="56"/>
+      <c r="G45" s="46"/>
+      <c r="H45" s="47"/>
+      <c r="I45" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="46" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C46" s="51"/>
-      <c r="D46" s="49"/>
-      <c r="E46" s="50"/>
-      <c r="F46" s="61"/>
-      <c r="G46" s="51"/>
-      <c r="H46" s="52"/>
-      <c r="I46" s="46" t="str">
+      <c r="C46" s="46"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="45"/>
+      <c r="F46" s="56"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="47"/>
+      <c r="I46" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="47" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C47" s="51"/>
-      <c r="D47" s="49"/>
-      <c r="E47" s="50"/>
-      <c r="F47" s="61"/>
-      <c r="G47" s="51"/>
-      <c r="H47" s="52"/>
-      <c r="I47" s="46" t="str">
+      <c r="C47" s="46"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="56"/>
+      <c r="G47" s="46"/>
+      <c r="H47" s="47"/>
+      <c r="I47" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="48" spans="3:20" ht="16" x14ac:dyDescent="0.35">
-      <c r="C48" s="51"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="50"/>
-      <c r="F48" s="61"/>
-      <c r="G48" s="51"/>
-      <c r="H48" s="52"/>
-      <c r="I48" s="46" t="str">
+      <c r="C48" s="46"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="45"/>
+      <c r="F48" s="56"/>
+      <c r="G48" s="46"/>
+      <c r="H48" s="47"/>
+      <c r="I48" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C49" s="51"/>
-      <c r="D49" s="49"/>
-      <c r="E49" s="50"/>
-      <c r="F49" s="61"/>
-      <c r="G49" s="51"/>
-      <c r="H49" s="52"/>
-      <c r="I49" s="46" t="str">
+      <c r="C49" s="46"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="45"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="46"/>
+      <c r="H49" s="47"/>
+      <c r="I49" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="50" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C50" s="51"/>
-      <c r="D50" s="49"/>
-      <c r="E50" s="50"/>
-      <c r="F50" s="61"/>
-      <c r="G50" s="51"/>
-      <c r="H50" s="52"/>
-      <c r="I50" s="46" t="str">
+      <c r="C50" s="46"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="56"/>
+      <c r="G50" s="46"/>
+      <c r="H50" s="47"/>
+      <c r="I50" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="51" spans="3:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="C51" s="51"/>
-      <c r="D51" s="49"/>
-      <c r="E51" s="53"/>
-      <c r="F51" s="61"/>
-      <c r="G51" s="51"/>
-      <c r="H51" s="52"/>
-      <c r="I51" s="47"/>
+      <c r="C51" s="46"/>
+      <c r="D51" s="44"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="56"/>
+      <c r="G51" s="46"/>
+      <c r="H51" s="47"/>
+      <c r="I51" s="42"/>
     </row>
     <row r="52" spans="3:9" x14ac:dyDescent="0.35"/>
     <row r="53" spans="3:9" x14ac:dyDescent="0.35"/>
     <row r="54" spans="3:9" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <sheetProtection sheet="1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="C12:I12"/>
   </mergeCells>
@@ -27838,63 +27789,63 @@
   <dimension ref="A1:M54"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.90625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="21.453125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="18.36328125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="13.7265625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="12.6328125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="21" style="5" customWidth="1"/>
-    <col min="8" max="8" width="15" style="5" customWidth="1"/>
-    <col min="9" max="9" width="8.7265625" style="5" customWidth="1"/>
-    <col min="10" max="10" width="8.7265625" style="5" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="11.36328125" style="35" hidden="1" customWidth="1"/>
-    <col min="12" max="13" width="11.36328125" style="5" hidden="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.7265625" style="5" hidden="1"/>
+    <col min="1" max="1" width="29.90625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.7265625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="18.36328125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="12.6328125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="21" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15" style="3" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="8.7265625" style="3" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="11.36328125" style="31" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="11.36328125" style="3" hidden="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.7265625" style="3" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="I2" s="40"/>
+      <c r="I2" s="36"/>
     </row>
     <row r="3" spans="1:11" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="I3" s="62">
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="I3" s="57">
         <f>COUNTA(C14:C112)</f>
         <v>10</v>
       </c>
-      <c r="K3" s="37" t="e">
+      <c r="K3" s="33" t="e">
         <f>SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="I4" s="62">
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="I4" s="57">
         <f>COUNTIFS(C14:C112,"&lt;&gt;",F14:F112,"SIM")</f>
         <v>8</v>
       </c>
-      <c r="K4" s="37">
+      <c r="K4" s="33">
         <f>SUM(H:H)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="I5" s="62">
+      <c r="I5" s="57">
         <f>COUNTIF(H14:H112,"PENDENTE")+COUNTIF(H14:H112,"INCOMPLETO")</f>
         <v>2</v>
       </c>
-      <c r="K5" s="40" t="e">
+      <c r="K5" s="36" t="e">
         <f>COUNTIF(DOCUMENTOS!#REF!,"PENDENTE")+COUNTIF(DOCUMENTOS!#REF!,"INCOMPLETO")</f>
         <v>#REF!</v>
       </c>
@@ -27905,548 +27856,548 @@
     <row r="9" spans="1:11" x14ac:dyDescent="0.35"/>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35"/>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="1:11" s="42" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="41"/>
-      <c r="C12" s="43" t="s">
+    <row r="12" spans="1:11" s="38" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="37"/>
+      <c r="C12" s="84" t="s">
         <v>236</v>
       </c>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="K12" s="44"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="K12" s="39"/>
     </row>
     <row r="13" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="88" t="s">
+      <c r="C13" s="78" t="s">
         <v>173</v>
       </c>
-      <c r="D13" s="88" t="s">
+      <c r="D13" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="88" t="s">
+      <c r="E13" s="78" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="88" t="s">
+      <c r="F13" s="78" t="s">
         <v>174</v>
       </c>
-      <c r="G13" s="88" t="s">
+      <c r="G13" s="78" t="s">
         <v>175</v>
       </c>
-      <c r="H13" s="88" t="s">
+      <c r="H13" s="78" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="C14" s="63" t="s">
+      <c r="C14" s="58" t="s">
         <v>186</v>
       </c>
-      <c r="D14" s="51" t="s">
+      <c r="D14" s="46" t="s">
         <v>178</v>
       </c>
-      <c r="E14" s="54">
+      <c r="E14" s="49">
         <v>2025</v>
       </c>
-      <c r="F14" s="61" t="s">
+      <c r="F14" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="64" t="s">
+      <c r="G14" s="59" t="s">
         <v>194</v>
       </c>
-      <c r="H14" s="46" t="str">
+      <c r="H14" s="41" t="str">
         <f t="shared" ref="H14:H24" si="0">IF(COUNTA(C14:G14)=0,"",IF(OR(C14="",D14="",E14="",F14=""),"INCOMPLETO",IF(F14="NÃO","PENDENTE",IF(G14="","INCOMPLETO","CONCLUÍDO"))))</f>
         <v>CONCLUÍDO</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="C15" s="63" t="s">
+      <c r="C15" s="58" t="s">
         <v>187</v>
       </c>
-      <c r="D15" s="51" t="s">
+      <c r="D15" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="E15" s="54">
+      <c r="E15" s="49">
         <v>2025</v>
       </c>
-      <c r="F15" s="61" t="s">
+      <c r="F15" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="G15" s="64" t="s">
+      <c r="G15" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="H15" s="46" t="str">
+      <c r="H15" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="16" x14ac:dyDescent="0.35">
-      <c r="C16" s="63" t="s">
+      <c r="C16" s="58" t="s">
         <v>188</v>
       </c>
-      <c r="D16" s="51" t="s">
+      <c r="D16" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="E16" s="54">
+      <c r="E16" s="49">
         <v>2025</v>
       </c>
-      <c r="F16" s="61" t="s">
+      <c r="F16" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="64" t="s">
+      <c r="G16" s="59" t="s">
         <v>196</v>
       </c>
-      <c r="H16" s="46" t="str">
+      <c r="H16" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
     </row>
     <row r="17" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C17" s="63" t="s">
+      <c r="C17" s="58" t="s">
         <v>189</v>
       </c>
-      <c r="D17" s="51" t="s">
+      <c r="D17" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="E17" s="54">
+      <c r="E17" s="49">
         <v>2025</v>
       </c>
-      <c r="F17" s="61" t="s">
+      <c r="F17" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="G17" s="64" t="s">
+      <c r="G17" s="59" t="s">
         <v>197</v>
       </c>
-      <c r="H17" s="46" t="str">
+      <c r="H17" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
     </row>
     <row r="18" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C18" s="63" t="s">
+      <c r="C18" s="58" t="s">
         <v>190</v>
       </c>
-      <c r="D18" s="51" t="s">
+      <c r="D18" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="E18" s="54">
+      <c r="E18" s="49">
         <v>2025</v>
       </c>
-      <c r="F18" s="61" t="s">
+      <c r="F18" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="G18" s="64"/>
-      <c r="H18" s="46" t="str">
+      <c r="G18" s="59"/>
+      <c r="H18" s="41" t="str">
         <f t="shared" si="0"/>
         <v>PENDENTE</v>
       </c>
     </row>
     <row r="19" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C19" s="63" t="s">
+      <c r="C19" s="58" t="s">
         <v>182</v>
       </c>
-      <c r="D19" s="51" t="s">
+      <c r="D19" s="46" t="s">
         <v>183</v>
       </c>
-      <c r="E19" s="54">
+      <c r="E19" s="49">
         <v>2025</v>
       </c>
-      <c r="F19" s="61" t="s">
+      <c r="F19" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="G19" s="64" t="s">
+      <c r="G19" s="59" t="s">
         <v>198</v>
       </c>
-      <c r="H19" s="46" t="str">
+      <c r="H19" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
     </row>
     <row r="20" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C20" s="63" t="s">
+      <c r="C20" s="58" t="s">
         <v>184</v>
       </c>
-      <c r="D20" s="51" t="s">
+      <c r="D20" s="46" t="s">
         <v>183</v>
       </c>
-      <c r="E20" s="54">
+      <c r="E20" s="49">
         <v>2025</v>
       </c>
-      <c r="F20" s="61" t="s">
+      <c r="F20" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="64" t="s">
+      <c r="G20" s="59" t="s">
         <v>199</v>
       </c>
-      <c r="H20" s="46" t="str">
+      <c r="H20" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
     </row>
     <row r="21" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C21" s="63" t="s">
+      <c r="C21" s="58" t="s">
         <v>191</v>
       </c>
-      <c r="D21" s="51" t="s">
+      <c r="D21" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="E21" s="54">
+      <c r="E21" s="49">
         <v>2025</v>
       </c>
-      <c r="F21" s="61" t="s">
+      <c r="F21" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="G21" s="64"/>
-      <c r="H21" s="46" t="str">
+      <c r="G21" s="59"/>
+      <c r="H21" s="41" t="str">
         <f t="shared" si="0"/>
         <v>PENDENTE</v>
       </c>
     </row>
     <row r="22" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C22" s="63" t="s">
+      <c r="C22" s="58" t="s">
         <v>192</v>
       </c>
-      <c r="D22" s="51" t="s">
+      <c r="D22" s="46" t="s">
         <v>185</v>
       </c>
-      <c r="E22" s="54">
+      <c r="E22" s="49">
         <v>2025</v>
       </c>
-      <c r="F22" s="61" t="s">
+      <c r="F22" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="64" t="s">
+      <c r="G22" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="H22" s="46" t="str">
+      <c r="H22" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
     </row>
     <row r="23" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C23" s="63" t="s">
+      <c r="C23" s="58" t="s">
         <v>193</v>
       </c>
-      <c r="D23" s="51" t="s">
+      <c r="D23" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="E23" s="54">
+      <c r="E23" s="49">
         <v>2025</v>
       </c>
-      <c r="F23" s="61" t="s">
+      <c r="F23" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="65" t="s">
+      <c r="G23" s="60" t="s">
         <v>201</v>
       </c>
-      <c r="H23" s="46" t="str">
+      <c r="H23" s="41" t="str">
         <f t="shared" si="0"/>
         <v>CONCLUÍDO</v>
       </c>
     </row>
     <row r="24" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C24" s="48"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="61"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="46" t="str">
+      <c r="C24" s="43"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="25" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C25" s="48"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="61"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="46" t="str">
+      <c r="C25" s="43"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="41" t="str">
         <f t="shared" ref="H25:H51" si="1">IF(COUNTA(C25:G25)=0,"",IF(OR(C25="",D25="",E25="",F25=""),"INCOMPLETO",IF(F25="NÃO","PENDENTE",IF(G25="","INCOMPLETO","CONCLUÍDO"))))</f>
         <v/>
       </c>
     </row>
     <row r="26" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C26" s="51"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="61"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="46" t="str">
+      <c r="C26" s="46"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="27" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C27" s="51"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="55"/>
-      <c r="F27" s="61"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="46" t="str">
+      <c r="C27" s="46"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="28" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C28" s="51"/>
-      <c r="D28" s="49"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="61"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="46" t="str">
+      <c r="C28" s="46"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="29" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C29" s="51"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="55"/>
-      <c r="F29" s="61"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="46" t="str">
+      <c r="C29" s="46"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="30" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C30" s="51"/>
-      <c r="D30" s="49"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="46" t="str">
+      <c r="C30" s="46"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="31" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C31" s="51"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="46" t="str">
+      <c r="C31" s="46"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="56"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="32" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C32" s="51"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="55"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="46" t="str">
+      <c r="C32" s="46"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="56"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="33" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C33" s="51"/>
-      <c r="D33" s="49"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="61"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="46" t="str">
+      <c r="C33" s="46"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="34" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C34" s="51"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="55"/>
-      <c r="F34" s="61"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="46" t="str">
+      <c r="C34" s="46"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="56"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="35" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C35" s="51"/>
-      <c r="D35" s="49"/>
-      <c r="E35" s="55"/>
-      <c r="F35" s="61"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="46" t="str">
+      <c r="C35" s="46"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="36" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C36" s="51"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="61"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="46" t="str">
+      <c r="C36" s="46"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="56"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="37" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C37" s="51"/>
-      <c r="D37" s="49"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="61"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="46" t="str">
+      <c r="C37" s="46"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="50"/>
+      <c r="F37" s="56"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="38" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C38" s="51"/>
-      <c r="D38" s="49"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="51"/>
-      <c r="H38" s="46" t="str">
+      <c r="C38" s="46"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="50"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="39" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C39" s="51"/>
-      <c r="D39" s="49"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="46" t="str">
+      <c r="C39" s="46"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="46"/>
+      <c r="H39" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="40" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C40" s="51"/>
-      <c r="D40" s="49"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="51"/>
-      <c r="H40" s="46" t="str">
+      <c r="C40" s="46"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="50"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="46"/>
+      <c r="H40" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="41" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C41" s="51"/>
-      <c r="D41" s="49"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="51"/>
-      <c r="H41" s="46" t="str">
+      <c r="C41" s="46"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="50"/>
+      <c r="F41" s="56"/>
+      <c r="G41" s="46"/>
+      <c r="H41" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="42" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C42" s="51"/>
-      <c r="D42" s="49"/>
-      <c r="E42" s="55"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="51"/>
-      <c r="H42" s="46" t="str">
+      <c r="C42" s="46"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="46"/>
+      <c r="H42" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="43" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C43" s="51"/>
-      <c r="D43" s="49"/>
-      <c r="E43" s="55"/>
-      <c r="F43" s="61"/>
-      <c r="G43" s="51"/>
-      <c r="H43" s="46" t="str">
+      <c r="C43" s="46"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="50"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="46"/>
+      <c r="H43" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="44" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C44" s="51"/>
-      <c r="D44" s="49"/>
-      <c r="E44" s="55"/>
-      <c r="F44" s="61"/>
-      <c r="G44" s="51"/>
-      <c r="H44" s="46" t="str">
+      <c r="C44" s="46"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="56"/>
+      <c r="G44" s="46"/>
+      <c r="H44" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="45" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C45" s="51"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="61"/>
-      <c r="G45" s="51"/>
-      <c r="H45" s="46" t="str">
+      <c r="C45" s="46"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="50"/>
+      <c r="F45" s="56"/>
+      <c r="G45" s="46"/>
+      <c r="H45" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="46" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C46" s="51"/>
-      <c r="D46" s="49"/>
-      <c r="E46" s="55"/>
-      <c r="F46" s="61"/>
-      <c r="G46" s="51"/>
-      <c r="H46" s="46" t="str">
+      <c r="C46" s="46"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="50"/>
+      <c r="F46" s="56"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="47" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C47" s="51"/>
-      <c r="D47" s="49"/>
-      <c r="E47" s="55"/>
-      <c r="F47" s="61"/>
-      <c r="G47" s="51"/>
-      <c r="H47" s="46" t="str">
+      <c r="C47" s="46"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="50"/>
+      <c r="F47" s="56"/>
+      <c r="G47" s="46"/>
+      <c r="H47" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="48" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C48" s="51"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="55"/>
-      <c r="F48" s="61"/>
-      <c r="G48" s="51"/>
-      <c r="H48" s="46" t="str">
+      <c r="C48" s="46"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="50"/>
+      <c r="F48" s="56"/>
+      <c r="G48" s="46"/>
+      <c r="H48" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C49" s="51"/>
-      <c r="D49" s="49"/>
-      <c r="E49" s="55"/>
-      <c r="F49" s="61"/>
-      <c r="G49" s="51"/>
-      <c r="H49" s="46" t="str">
+      <c r="C49" s="46"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="46"/>
+      <c r="H49" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="50" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C50" s="51"/>
-      <c r="D50" s="49"/>
-      <c r="E50" s="55"/>
-      <c r="F50" s="61"/>
-      <c r="G50" s="51"/>
-      <c r="H50" s="46" t="str">
+      <c r="C50" s="46"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="50"/>
+      <c r="F50" s="56"/>
+      <c r="G50" s="46"/>
+      <c r="H50" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="51" spans="3:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="C51" s="51"/>
-      <c r="D51" s="49"/>
-      <c r="E51" s="53"/>
-      <c r="F51" s="61"/>
-      <c r="G51" s="51"/>
-      <c r="H51" s="46" t="str">
+      <c r="C51" s="46"/>
+      <c r="D51" s="44"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="56"/>
+      <c r="G51" s="46"/>
+      <c r="H51" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -28455,7 +28406,7 @@
     <row r="53" spans="3:8" x14ac:dyDescent="0.35"/>
     <row r="54" spans="3:8" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <sheetProtection sheet="1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="C12:H12"/>
   </mergeCells>
@@ -28495,415 +28446,415 @@
   <sheetPr>
     <tabColor rgb="FF17324D"/>
   </sheetPr>
-  <dimension ref="A1:XFD54"/>
+  <dimension ref="A1:XFC54"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.90625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="21.453125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="18.36328125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="13.7265625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="12.6328125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="21" style="5" customWidth="1"/>
-    <col min="8" max="8" width="15" style="5" customWidth="1"/>
-    <col min="9" max="9" width="9.54296875" style="5" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="8.7265625" style="67" customWidth="1"/>
-    <col min="11" max="11" width="8.7265625" style="67" hidden="1"/>
-    <col min="12" max="12" width="11.36328125" style="67" hidden="1"/>
-    <col min="13" max="14" width="11.36328125" style="68" hidden="1"/>
-    <col min="15" max="16383" width="8.7265625" style="68" hidden="1"/>
-    <col min="16384" max="16384" width="7.7265625" style="68" hidden="1"/>
+    <col min="1" max="1" width="29.90625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.7265625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="18.36328125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="12.6328125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="21" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9.54296875" style="3" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="8.7265625" style="61" customWidth="1"/>
+    <col min="11" max="11" width="8.7265625" style="61" hidden="1"/>
+    <col min="12" max="12" width="11.36328125" style="61" hidden="1"/>
+    <col min="13" max="14" width="11.36328125" style="3" hidden="1"/>
+    <col min="15" max="16383" width="8.7265625" style="3" hidden="1"/>
+    <col min="16384" max="16384" width="7.7265625" style="3" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="I1" s="66"/>
+      <c r="I1" s="61"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="I2" s="69">
+      <c r="I2" s="62">
         <f>SUM(RENDIMENTOS!G:G)</f>
         <v>27006.3</v>
       </c>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="I3" s="69">
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="I3" s="62">
         <f>SUM(PAGAMENTOS!G:G)</f>
         <v>7570</v>
       </c>
-      <c r="L3" s="94"/>
-      <c r="M3" s="93"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="80"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="34" t="s">
         <v>203</v>
       </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="I4" s="69">
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="I4" s="62">
         <f>SUM('BENS E DIREITOS'!H:H)</f>
         <v>249500</v>
       </c>
-      <c r="L4" s="94"/>
-      <c r="M4" s="93"/>
+      <c r="L4" s="83"/>
+      <c r="M4" s="80"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="I5" s="69">
+      <c r="I5" s="62">
         <f>BANCOS!F7</f>
         <v>25971.35</v>
       </c>
-      <c r="L5" s="93"/>
-      <c r="M5" s="93"/>
+      <c r="L5" s="80"/>
+      <c r="M5" s="80"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="I6" s="70" t="str">
+      <c r="I6" s="63" t="str">
         <f>COUNTIF(DOCUMENTOS!F14:F112,"SIM")&amp;" de "&amp;COUNTA(DOCUMENTOS!C14:C112)</f>
         <v>8 de 10</v>
       </c>
-      <c r="L6" s="93"/>
-      <c r="M6" s="93"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="I7" s="70">
+      <c r="I7" s="63">
         <f>COUNTIF(BANCOS!D21:D47,"PENDENTE")+COUNTIF(BANCOS!D21:D47,"INCOMPLETO")+COUNTIF(RENDIMENTOS!I:I,"INCOMPLETO")+COUNTIF(PAGAMENTOS!I:I,"INCOMPLETO")+COUNTIF('BENS E DIREITOS'!I:I,"INCOMPLETO")+COUNTIF(DOCUMENTOS!H:H,"PENDENTE")+COUNTIF(DOCUMENTOS!H:H,"INCOMPLETO")</f>
         <v>6</v>
       </c>
-      <c r="L7" s="93"/>
-      <c r="M7" s="93"/>
+      <c r="L7" s="80"/>
+      <c r="M7" s="80"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="L8" s="93"/>
-      <c r="M8" s="93"/>
+      <c r="L8" s="80"/>
+      <c r="M8" s="80"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="L9" s="93"/>
-      <c r="M9" s="93"/>
+      <c r="L9" s="80"/>
+      <c r="M9" s="80"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="I10" s="40"/>
-      <c r="L10" s="93"/>
-      <c r="M10" s="93"/>
+      <c r="I10" s="36"/>
+      <c r="L10" s="80"/>
+      <c r="M10" s="80"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="I11" s="40" t="s">
+      <c r="I11" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="J11" s="67" t="s">
+      <c r="J11" s="61" t="s">
         <v>65</v>
       </c>
-      <c r="L11" s="93"/>
-      <c r="M11" s="93"/>
-    </row>
-    <row r="12" spans="1:14" s="73" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="41"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="40" t="s">
+      <c r="L11" s="80"/>
+      <c r="M11" s="80"/>
+    </row>
+    <row r="12" spans="1:14" s="38" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="37"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="J12" s="71">
+      <c r="J12" s="64">
         <f>I2</f>
         <v>27006.3</v>
       </c>
-      <c r="K12" s="72"/>
-      <c r="L12" s="95"/>
-      <c r="M12" s="95"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="82"/>
+      <c r="M12" s="82"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="I13" s="40" t="s">
+      <c r="I13" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="J13" s="71">
+      <c r="J13" s="64">
         <f>I3</f>
         <v>7570</v>
       </c>
-      <c r="L13" s="93"/>
-      <c r="M13" s="93"/>
+      <c r="L13" s="80"/>
+      <c r="M13" s="80"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="I14" s="40"/>
-      <c r="L14" s="93"/>
-      <c r="M14" s="93"/>
+      <c r="I14" s="36"/>
+      <c r="L14" s="80"/>
+      <c r="M14" s="80"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="I15" s="67"/>
-      <c r="M15" s="67"/>
-      <c r="N15" s="67"/>
+      <c r="I15" s="61"/>
+      <c r="M15" s="61"/>
+      <c r="N15" s="61"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="I16" s="67" t="s">
+      <c r="I16" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="J16" s="67" t="s">
+      <c r="J16" s="61" t="s">
         <v>204</v>
       </c>
-      <c r="M16" s="67"/>
-      <c r="N16" s="67"/>
+      <c r="M16" s="61"/>
+      <c r="N16" s="61"/>
     </row>
     <row r="17" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I17" s="67" t="s">
+      <c r="I17" s="61" t="s">
         <v>205</v>
       </c>
-      <c r="J17" s="67">
+      <c r="J17" s="61">
         <f>COUNTIF(DOCUMENTOS!F:F,"SIM")</f>
         <v>8</v>
       </c>
-      <c r="M17" s="67"/>
-      <c r="N17" s="67"/>
+      <c r="M17" s="61"/>
+      <c r="N17" s="61"/>
     </row>
     <row r="18" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I18" s="67" t="s">
+      <c r="I18" s="61" t="s">
         <v>206</v>
       </c>
-      <c r="J18" s="67">
+      <c r="J18" s="61">
         <f>COUNTIF(DOCUMENTOS!F:F,"NÃO")</f>
         <v>2</v>
       </c>
-      <c r="M18" s="67"/>
-      <c r="N18" s="67"/>
+      <c r="M18" s="61"/>
+      <c r="N18" s="61"/>
     </row>
     <row r="19" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I19" s="67"/>
-      <c r="M19" s="67"/>
-      <c r="N19" s="67"/>
+      <c r="I19" s="61"/>
+      <c r="M19" s="61"/>
+      <c r="N19" s="61"/>
     </row>
     <row r="20" spans="9:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="I20" s="74" t="s">
+      <c r="I20" s="66" t="s">
         <v>207</v>
       </c>
-      <c r="J20" s="74" t="s">
+      <c r="J20" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="74" t="s">
+      <c r="K20" s="66" t="s">
         <v>208</v>
       </c>
-      <c r="L20" s="74" t="s">
+      <c r="L20" s="66" t="s">
         <v>214</v>
       </c>
-      <c r="M20" s="67"/>
-      <c r="N20" s="67"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="61"/>
     </row>
     <row r="21" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I21" s="75" t="s">
+      <c r="I21" s="67" t="s">
         <v>209</v>
       </c>
-      <c r="J21" s="75">
+      <c r="J21" s="67">
         <v>3</v>
       </c>
-      <c r="K21" s="75">
+      <c r="K21" s="67">
         <v>2</v>
       </c>
-      <c r="L21" s="76">
+      <c r="L21" s="68">
         <f>IF(J21=0,0,(J21-K21)/J21)</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M21" s="77">
+      <c r="M21" s="69">
         <f>1-L21</f>
         <v>0.66666666666666674</v>
       </c>
-      <c r="N21" s="67"/>
+      <c r="N21" s="61"/>
     </row>
     <row r="22" spans="9:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="I22" s="75" t="s">
+      <c r="I22" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="J22" s="75">
+      <c r="J22" s="67">
         <v>10</v>
       </c>
-      <c r="K22" s="75">
+      <c r="K22" s="67">
         <v>1</v>
       </c>
-      <c r="L22" s="76">
+      <c r="L22" s="68">
         <f>IF(J22=0,0,(J22-K22)/J22)</f>
         <v>0.9</v>
       </c>
-      <c r="M22" s="77">
+      <c r="M22" s="69">
         <f>1-L22</f>
         <v>9.9999999999999978E-2</v>
       </c>
-      <c r="N22" s="67"/>
+      <c r="N22" s="61"/>
     </row>
     <row r="23" spans="9:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="I23" s="75" t="s">
+      <c r="I23" s="67" t="s">
         <v>211</v>
       </c>
-      <c r="J23" s="75">
+      <c r="J23" s="67">
         <v>10</v>
       </c>
-      <c r="K23" s="75">
+      <c r="K23" s="67">
         <v>0</v>
       </c>
-      <c r="L23" s="76">
+      <c r="L23" s="68">
         <f>IF(J23=0,0,(J23-K23)/J23)</f>
         <v>1</v>
       </c>
-      <c r="M23" s="77">
+      <c r="M23" s="69">
         <f>1-L23</f>
         <v>0</v>
       </c>
-      <c r="N23" s="67"/>
+      <c r="N23" s="61"/>
     </row>
     <row r="24" spans="9:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="I24" s="75" t="s">
+      <c r="I24" s="67" t="s">
         <v>212</v>
       </c>
-      <c r="J24" s="75">
+      <c r="J24" s="67">
         <v>5</v>
       </c>
-      <c r="K24" s="75">
+      <c r="K24" s="67">
         <v>1</v>
       </c>
-      <c r="L24" s="76">
+      <c r="L24" s="68">
         <f>IF(J24=0,0,(J24-K24)/J24)</f>
         <v>0.8</v>
       </c>
-      <c r="M24" s="77">
+      <c r="M24" s="69">
         <f>1-L24</f>
         <v>0.19999999999999996</v>
       </c>
-      <c r="N24" s="67"/>
+      <c r="N24" s="61"/>
     </row>
     <row r="25" spans="9:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="I25" s="75" t="s">
+      <c r="I25" s="67" t="s">
         <v>213</v>
       </c>
-      <c r="J25" s="75">
+      <c r="J25" s="67">
         <v>10</v>
       </c>
-      <c r="K25" s="75">
+      <c r="K25" s="67">
         <v>2</v>
       </c>
-      <c r="L25" s="76">
+      <c r="L25" s="68">
         <f>IF(J25=0,0,(J25-K25)/J25)</f>
         <v>0.8</v>
       </c>
-      <c r="M25" s="77">
+      <c r="M25" s="69">
         <f>1-L25</f>
         <v>0.19999999999999996</v>
       </c>
-      <c r="N25" s="67"/>
+      <c r="N25" s="61"/>
     </row>
     <row r="26" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I26" s="67"/>
-      <c r="M26" s="67"/>
-      <c r="N26" s="67"/>
+      <c r="I26" s="61"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="61"/>
     </row>
     <row r="27" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I27" s="67"/>
-      <c r="M27" s="67"/>
-      <c r="N27" s="67"/>
+      <c r="I27" s="61"/>
+      <c r="M27" s="61"/>
+      <c r="N27" s="61"/>
     </row>
     <row r="28" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I28" s="67"/>
-      <c r="M28" s="67"/>
-      <c r="N28" s="67"/>
+      <c r="I28" s="61"/>
+      <c r="M28" s="61"/>
+      <c r="N28" s="61"/>
     </row>
     <row r="29" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I29" s="67"/>
-      <c r="M29" s="67"/>
-      <c r="N29" s="67"/>
+      <c r="I29" s="61"/>
+      <c r="M29" s="61"/>
+      <c r="N29" s="61"/>
     </row>
     <row r="30" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I30" s="67"/>
-      <c r="M30" s="67"/>
-      <c r="N30" s="67"/>
+      <c r="I30" s="61"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="61"/>
     </row>
     <row r="31" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I31" s="67"/>
-      <c r="M31" s="67"/>
-      <c r="N31" s="67"/>
+      <c r="I31" s="61"/>
+      <c r="M31" s="61"/>
+      <c r="N31" s="61"/>
     </row>
     <row r="32" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I32" s="67"/>
-      <c r="M32" s="67"/>
-      <c r="N32" s="67"/>
+      <c r="I32" s="61"/>
+      <c r="M32" s="61"/>
+      <c r="N32" s="61"/>
     </row>
     <row r="33" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I33" s="67"/>
-      <c r="M33" s="67"/>
-      <c r="N33" s="67"/>
+      <c r="I33" s="61"/>
+      <c r="M33" s="61"/>
+      <c r="N33" s="61"/>
     </row>
     <row r="34" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I34" s="67"/>
-      <c r="M34" s="67"/>
-      <c r="N34" s="67"/>
+      <c r="I34" s="61"/>
+      <c r="M34" s="61"/>
+      <c r="N34" s="61"/>
     </row>
     <row r="35" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I35" s="67"/>
-      <c r="M35" s="67"/>
-      <c r="N35" s="67"/>
+      <c r="I35" s="61"/>
+      <c r="M35" s="61"/>
+      <c r="N35" s="61"/>
     </row>
     <row r="36" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I36" s="67"/>
-      <c r="M36" s="67"/>
-      <c r="N36" s="67"/>
+      <c r="I36" s="61"/>
+      <c r="M36" s="61"/>
+      <c r="N36" s="61"/>
     </row>
     <row r="37" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I37" s="67"/>
-      <c r="M37" s="67"/>
-      <c r="N37" s="67"/>
+      <c r="I37" s="61"/>
+      <c r="M37" s="61"/>
+      <c r="N37" s="61"/>
     </row>
     <row r="38" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I38" s="67"/>
-      <c r="M38" s="67"/>
-      <c r="N38" s="67"/>
+      <c r="I38" s="61"/>
+      <c r="M38" s="61"/>
+      <c r="N38" s="61"/>
     </row>
     <row r="39" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I39" s="67"/>
-      <c r="M39" s="67"/>
-      <c r="N39" s="67"/>
+      <c r="I39" s="61"/>
+      <c r="M39" s="61"/>
+      <c r="N39" s="61"/>
     </row>
     <row r="40" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I40" s="67"/>
-      <c r="M40" s="67"/>
-      <c r="N40" s="67"/>
+      <c r="I40" s="61"/>
+      <c r="M40" s="61"/>
+      <c r="N40" s="61"/>
     </row>
     <row r="41" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I41" s="67"/>
-      <c r="M41" s="67"/>
-      <c r="N41" s="67"/>
+      <c r="I41" s="61"/>
+      <c r="M41" s="61"/>
+      <c r="N41" s="61"/>
     </row>
     <row r="42" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I42" s="67"/>
-      <c r="M42" s="67"/>
-      <c r="N42" s="67"/>
+      <c r="I42" s="61"/>
+      <c r="M42" s="61"/>
+      <c r="N42" s="61"/>
     </row>
     <row r="43" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I43" s="67"/>
-      <c r="M43" s="67"/>
-      <c r="N43" s="67"/>
+      <c r="I43" s="61"/>
+      <c r="M43" s="61"/>
+      <c r="N43" s="61"/>
     </row>
     <row r="44" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I44" s="67"/>
-      <c r="M44" s="67"/>
-      <c r="N44" s="67"/>
+      <c r="I44" s="61"/>
+      <c r="M44" s="61"/>
+      <c r="N44" s="61"/>
     </row>
     <row r="45" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I45" s="67"/>
-      <c r="M45" s="67"/>
-      <c r="N45" s="67"/>
+      <c r="I45" s="61"/>
+      <c r="M45" s="61"/>
+      <c r="N45" s="61"/>
     </row>
     <row r="46" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I46" s="67"/>
-      <c r="M46" s="67"/>
-      <c r="N46" s="67"/>
+      <c r="I46" s="61"/>
+      <c r="M46" s="61"/>
+      <c r="N46" s="61"/>
     </row>
     <row r="47" spans="9:14" x14ac:dyDescent="0.35">
-      <c r="I47" s="67"/>
-      <c r="M47" s="67"/>
-      <c r="N47" s="67"/>
+      <c r="I47" s="61"/>
+      <c r="M47" s="61"/>
+      <c r="N47" s="61"/>
     </row>
     <row r="48" spans="9:14" x14ac:dyDescent="0.35"/>
     <row r="49" x14ac:dyDescent="0.35"/>
@@ -28913,7 +28864,7 @@
     <row r="53" x14ac:dyDescent="0.35"/>
     <row r="54" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <sheetProtection sheet="1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -28921,642 +28872,642 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1941554-A370-46DD-A9A9-42EFA6CCBA56}">
-  <dimension ref="A3:H57"/>
+  <dimension ref="A3:I57"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.90625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="30.08984375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="15.7265625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="16.54296875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="13.6328125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.36328125" style="5" customWidth="1"/>
-    <col min="8" max="8" width="17.1796875" style="5" customWidth="1"/>
-    <col min="9" max="9" width="5.7265625" style="5" customWidth="1"/>
-    <col min="10" max="16384" width="8.7265625" style="5" hidden="1"/>
+    <col min="1" max="1" width="29.90625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.7265625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="30.08984375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.7265625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="16.54296875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.6328125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="11.36328125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="5.7265625" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="8.7265625" style="3" hidden="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="3:8" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="34" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="7" spans="3:8" ht="32" x14ac:dyDescent="0.35">
-      <c r="C7" s="78" t="s">
+      <c r="C7" s="70" t="s">
         <v>209</v>
       </c>
-      <c r="D7" s="78" t="s">
+      <c r="D7" s="70" t="s">
         <v>233</v>
       </c>
-      <c r="E7" s="78" t="s">
+      <c r="E7" s="70" t="s">
         <v>232</v>
       </c>
-      <c r="F7" s="78" t="s">
+      <c r="F7" s="70" t="s">
         <v>231</v>
       </c>
-      <c r="G7" s="78" t="s">
+      <c r="G7" s="70" t="s">
         <v>230</v>
       </c>
-      <c r="H7" s="78" t="s">
+      <c r="H7" s="70" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="8" spans="3:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="C8" s="79" t="s">
+      <c r="C8" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="79" t="s">
+      <c r="D8" s="71" t="s">
         <v>108</v>
       </c>
-      <c r="E8" s="79" t="s">
+      <c r="E8" s="71" t="s">
         <v>122</v>
       </c>
-      <c r="F8" s="79" t="s">
+      <c r="F8" s="71" t="s">
         <v>140</v>
       </c>
-      <c r="G8" s="79" t="s">
+      <c r="G8" s="71" t="s">
         <v>162</v>
       </c>
-      <c r="H8" s="79" t="s">
+      <c r="H8" s="71" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="9" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C9" s="79" t="s">
+      <c r="C9" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="79" t="s">
+      <c r="D9" s="71" t="s">
         <v>107</v>
       </c>
-      <c r="E9" s="79" t="s">
+      <c r="E9" s="71" t="s">
         <v>228</v>
       </c>
-      <c r="F9" s="79" t="s">
+      <c r="F9" s="71" t="s">
         <v>138</v>
       </c>
-      <c r="G9" s="79" t="s">
+      <c r="G9" s="71" t="s">
         <v>165</v>
       </c>
-      <c r="H9" s="79" t="s">
+      <c r="H9" s="71" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="10" spans="3:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="79" t="s">
+      <c r="D10" s="71" t="s">
         <v>227</v>
       </c>
-      <c r="E10" s="79" t="s">
+      <c r="E10" s="71" t="s">
         <v>226</v>
       </c>
-      <c r="F10" s="79" t="s">
+      <c r="F10" s="71" t="s">
         <v>143</v>
       </c>
-      <c r="G10" s="79" t="s">
+      <c r="G10" s="71" t="s">
         <v>225</v>
       </c>
-      <c r="H10" s="79" t="s">
+      <c r="H10" s="71" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="11" spans="3:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="C11" s="79" t="s">
+      <c r="C11" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="79" t="s">
+      <c r="D11" s="71" t="s">
         <v>224</v>
       </c>
-      <c r="E11" s="79" t="s">
+      <c r="E11" s="71" t="s">
         <v>124</v>
       </c>
-      <c r="F11" s="79" t="s">
+      <c r="F11" s="71" t="s">
         <v>147</v>
       </c>
-      <c r="G11" s="79" t="s">
+      <c r="G11" s="71" t="s">
         <v>167</v>
       </c>
-      <c r="H11" s="79" t="s">
+      <c r="H11" s="71" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="12" spans="3:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="C12" s="79" t="s">
+      <c r="C12" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="79" t="s">
+      <c r="D12" s="71" t="s">
         <v>223</v>
       </c>
-      <c r="E12" s="79" t="s">
+      <c r="E12" s="71" t="s">
         <v>126</v>
       </c>
-      <c r="F12" s="79" t="s">
+      <c r="F12" s="71" t="s">
         <v>149</v>
       </c>
-      <c r="G12" s="79" t="s">
+      <c r="G12" s="71" t="s">
         <v>169</v>
       </c>
-      <c r="H12" s="79" t="s">
+      <c r="H12" s="71" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="13" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C13" s="79" t="s">
+      <c r="C13" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="79" t="s">
+      <c r="D13" s="71" t="s">
         <v>222</v>
       </c>
-      <c r="E13" s="79" t="s">
+      <c r="E13" s="71" t="s">
         <v>221</v>
       </c>
-      <c r="F13" s="79" t="s">
+      <c r="F13" s="71" t="s">
         <v>151</v>
       </c>
-      <c r="G13" s="79" t="s">
+      <c r="G13" s="71" t="s">
         <v>220</v>
       </c>
-      <c r="H13" s="79" t="s">
+      <c r="H13" s="71" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="14" spans="3:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="C14" s="79" t="s">
+      <c r="C14" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="79" t="s">
+      <c r="D14" s="71" t="s">
         <v>219</v>
       </c>
-      <c r="E14" s="79" t="s">
+      <c r="E14" s="71" t="s">
         <v>130</v>
       </c>
-      <c r="F14" s="79" t="s">
+      <c r="F14" s="71" t="s">
         <v>145</v>
       </c>
-      <c r="G14" s="79" t="s">
+      <c r="G14" s="71" t="s">
         <v>171</v>
       </c>
-      <c r="H14" s="79" t="s">
+      <c r="H14" s="71" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="15" spans="3:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="C15" s="79" t="s">
+      <c r="C15" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="79" t="s">
+      <c r="D15" s="71" t="s">
         <v>218</v>
       </c>
-      <c r="E15" s="79" t="s">
+      <c r="E15" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="F15" s="79" t="s">
+      <c r="F15" s="71" t="s">
         <v>153</v>
       </c>
-      <c r="G15" s="79"/>
-      <c r="H15" s="79"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
     </row>
     <row r="16" spans="3:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="C16" s="79" t="s">
+      <c r="C16" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="79" t="s">
+      <c r="D16" s="71" t="s">
         <v>215</v>
       </c>
-      <c r="E16" s="79" t="s">
+      <c r="E16" s="71" t="s">
         <v>217</v>
       </c>
-      <c r="F16" s="79" t="s">
+      <c r="F16" s="71" t="s">
         <v>216</v>
       </c>
-      <c r="G16" s="79"/>
-      <c r="H16" s="79"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
     </row>
     <row r="17" spans="3:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="C17" s="79" t="s">
+      <c r="C17" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="79"/>
-      <c r="E17" s="79" t="s">
+      <c r="D17" s="71"/>
+      <c r="E17" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="F17" s="79" t="s">
+      <c r="F17" s="71" t="s">
         <v>215</v>
       </c>
-      <c r="G17" s="79"/>
-      <c r="H17" s="79"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
     </row>
     <row r="18" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C18" s="79" t="s">
+      <c r="C18" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79" t="s">
+      <c r="D18" s="71"/>
+      <c r="E18" s="71" t="s">
         <v>215</v>
       </c>
-      <c r="F18" s="79"/>
-      <c r="G18" s="79"/>
-      <c r="H18" s="79"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
     </row>
     <row r="19" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C19" s="79" t="s">
+      <c r="C19" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
-      <c r="F19" s="79"/>
-      <c r="G19" s="79"/>
-      <c r="H19" s="79"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
     </row>
     <row r="20" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C20" s="79" t="s">
+      <c r="C20" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="79"/>
-      <c r="H20" s="79"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
     </row>
     <row r="21" spans="3:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="C21" s="79" t="s">
+      <c r="C21" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="79"/>
-      <c r="G21" s="79"/>
-      <c r="H21" s="79"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
     </row>
     <row r="22" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C22" s="79" t="s">
+      <c r="C22" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="D22" s="79"/>
-      <c r="E22" s="79"/>
-      <c r="F22" s="79"/>
-      <c r="G22" s="79"/>
-      <c r="H22" s="79"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
     </row>
     <row r="23" spans="3:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="C23" s="79" t="s">
+      <c r="C23" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="79"/>
-      <c r="E23" s="79"/>
-      <c r="F23" s="79"/>
-      <c r="G23" s="79"/>
-      <c r="H23" s="79"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
     </row>
     <row r="24" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C24" s="79" t="s">
+      <c r="C24" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="79"/>
-      <c r="E24" s="79"/>
-      <c r="F24" s="79"/>
-      <c r="G24" s="79"/>
-      <c r="H24" s="79"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
     </row>
     <row r="25" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C25" s="79" t="s">
+      <c r="C25" s="71" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="79"/>
-      <c r="E25" s="79"/>
-      <c r="F25" s="79"/>
-      <c r="G25" s="79"/>
-      <c r="H25" s="79"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
     </row>
     <row r="26" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C26" s="79" t="s">
+      <c r="C26" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="79"/>
-      <c r="E26" s="79"/>
-      <c r="F26" s="79"/>
-      <c r="G26" s="79"/>
-      <c r="H26" s="79"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
     </row>
     <row r="27" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C27" s="79" t="s">
+      <c r="C27" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="79"/>
-      <c r="E27" s="79"/>
-      <c r="F27" s="79"/>
-      <c r="G27" s="79"/>
-      <c r="H27" s="79"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
     </row>
     <row r="28" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C28" s="79" t="s">
+      <c r="C28" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="79"/>
-      <c r="E28" s="79"/>
-      <c r="F28" s="79"/>
-      <c r="G28" s="79"/>
-      <c r="H28" s="79"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
     </row>
     <row r="29" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C29" s="79" t="s">
+      <c r="C29" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="79"/>
-      <c r="E29" s="79"/>
-      <c r="F29" s="79"/>
-      <c r="G29" s="79"/>
-      <c r="H29" s="79"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
     </row>
     <row r="30" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C30" s="79" t="s">
+      <c r="C30" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="79"/>
-      <c r="E30" s="79"/>
-      <c r="F30" s="79"/>
-      <c r="G30" s="79"/>
-      <c r="H30" s="79"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
     </row>
     <row r="31" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C31" s="79" t="s">
+      <c r="C31" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="D31" s="79"/>
-      <c r="E31" s="79"/>
-      <c r="F31" s="79"/>
-      <c r="G31" s="79"/>
-      <c r="H31" s="79"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
     </row>
     <row r="32" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C32" s="79" t="s">
+      <c r="C32" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="79"/>
-      <c r="E32" s="79"/>
-      <c r="F32" s="79"/>
-      <c r="G32" s="79"/>
-      <c r="H32" s="79"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
     </row>
     <row r="33" spans="3:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="C33" s="79" t="s">
+      <c r="C33" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="D33" s="79"/>
-      <c r="E33" s="79"/>
-      <c r="F33" s="79"/>
-      <c r="G33" s="79"/>
-      <c r="H33" s="79"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
     </row>
     <row r="34" spans="3:8" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="C34" s="79" t="s">
+      <c r="C34" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="D34" s="79"/>
-      <c r="E34" s="80"/>
-      <c r="F34" s="79"/>
-      <c r="G34" s="79"/>
-      <c r="H34" s="79"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
     </row>
     <row r="35" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C35" s="79" t="s">
+      <c r="C35" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="D35" s="79"/>
-      <c r="E35" s="79"/>
-      <c r="F35" s="79"/>
-      <c r="G35" s="79"/>
-      <c r="H35" s="79"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
     </row>
     <row r="36" spans="3:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="C36" s="79" t="s">
+      <c r="C36" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="D36" s="79"/>
-      <c r="E36" s="79"/>
-      <c r="F36" s="79"/>
-      <c r="G36" s="79"/>
-      <c r="H36" s="79"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
     </row>
     <row r="37" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C37" s="79" t="s">
+      <c r="C37" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="D37" s="79"/>
-      <c r="E37" s="79"/>
-      <c r="F37" s="79"/>
-      <c r="G37" s="79"/>
-      <c r="H37" s="79"/>
+      <c r="D37" s="71"/>
+      <c r="E37" s="71"/>
+      <c r="F37" s="71"/>
+      <c r="G37" s="71"/>
+      <c r="H37" s="71"/>
     </row>
     <row r="38" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C38" s="79" t="s">
+      <c r="C38" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="D38" s="79"/>
-      <c r="E38" s="79"/>
-      <c r="F38" s="79"/>
-      <c r="G38" s="79"/>
-      <c r="H38" s="79"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
     </row>
     <row r="39" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C39" s="79" t="s">
+      <c r="C39" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="D39" s="79"/>
-      <c r="E39" s="79"/>
-      <c r="F39" s="79"/>
-      <c r="G39" s="79"/>
-      <c r="H39" s="79"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
     </row>
     <row r="40" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C40" s="79" t="s">
+      <c r="C40" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="D40" s="79"/>
-      <c r="E40" s="79"/>
-      <c r="F40" s="79"/>
-      <c r="G40" s="79"/>
-      <c r="H40" s="79"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
     </row>
     <row r="41" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C41" s="79" t="s">
+      <c r="C41" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="D41" s="79"/>
-      <c r="E41" s="79"/>
-      <c r="F41" s="79"/>
-      <c r="G41" s="79"/>
-      <c r="H41" s="79"/>
+      <c r="D41" s="71"/>
+      <c r="E41" s="71"/>
+      <c r="F41" s="71"/>
+      <c r="G41" s="71"/>
+      <c r="H41" s="71"/>
     </row>
     <row r="42" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C42" s="79" t="s">
+      <c r="C42" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="D42" s="79"/>
-      <c r="E42" s="79"/>
-      <c r="F42" s="79"/>
-      <c r="G42" s="79"/>
-      <c r="H42" s="79"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
     </row>
     <row r="43" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C43" s="79" t="s">
+      <c r="C43" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="D43" s="79"/>
-      <c r="E43" s="79"/>
-      <c r="F43" s="79"/>
-      <c r="G43" s="79"/>
-      <c r="H43" s="79"/>
+      <c r="D43" s="71"/>
+      <c r="E43" s="71"/>
+      <c r="F43" s="71"/>
+      <c r="G43" s="71"/>
+      <c r="H43" s="71"/>
     </row>
     <row r="44" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C44" s="79" t="s">
+      <c r="C44" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="D44" s="79"/>
-      <c r="E44" s="79"/>
-      <c r="F44" s="79"/>
-      <c r="G44" s="79"/>
-      <c r="H44" s="79"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
     </row>
     <row r="45" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C45" s="79" t="s">
+      <c r="C45" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="D45" s="79"/>
-      <c r="E45" s="79"/>
-      <c r="F45" s="79"/>
-      <c r="G45" s="79"/>
-      <c r="H45" s="79"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="71"/>
     </row>
     <row r="46" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C46" s="79" t="s">
+      <c r="C46" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="D46" s="79"/>
-      <c r="E46" s="79"/>
-      <c r="F46" s="79"/>
-      <c r="G46" s="79"/>
-      <c r="H46" s="79"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
     </row>
     <row r="47" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C47" s="79" t="s">
+      <c r="C47" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="D47" s="79"/>
-      <c r="E47" s="79"/>
-      <c r="F47" s="79"/>
-      <c r="G47" s="79"/>
-      <c r="H47" s="79"/>
+      <c r="D47" s="71"/>
+      <c r="E47" s="71"/>
+      <c r="F47" s="71"/>
+      <c r="G47" s="71"/>
+      <c r="H47" s="71"/>
     </row>
     <row r="48" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C48" s="79" t="s">
+      <c r="C48" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="D48" s="79"/>
-      <c r="E48" s="79"/>
-      <c r="F48" s="79"/>
-      <c r="G48" s="79"/>
-      <c r="H48" s="79"/>
+      <c r="D48" s="71"/>
+      <c r="E48" s="71"/>
+      <c r="F48" s="71"/>
+      <c r="G48" s="71"/>
+      <c r="H48" s="71"/>
     </row>
     <row r="49" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C49" s="79" t="s">
+      <c r="C49" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="D49" s="79"/>
-      <c r="E49" s="79"/>
-      <c r="F49" s="79"/>
-      <c r="G49" s="79"/>
-      <c r="H49" s="79"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="71"/>
+      <c r="G49" s="71"/>
+      <c r="H49" s="71"/>
     </row>
     <row r="50" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C50" s="79" t="s">
+      <c r="C50" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="D50" s="79"/>
-      <c r="E50" s="79"/>
-      <c r="F50" s="79"/>
-      <c r="G50" s="79"/>
-      <c r="H50" s="79"/>
+      <c r="D50" s="71"/>
+      <c r="E50" s="71"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="71"/>
+      <c r="H50" s="71"/>
     </row>
     <row r="51" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C51" s="79" t="s">
+      <c r="C51" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="D51" s="79"/>
-      <c r="E51" s="79"/>
-      <c r="F51" s="79"/>
-      <c r="G51" s="79"/>
-      <c r="H51" s="79"/>
+      <c r="D51" s="71"/>
+      <c r="E51" s="71"/>
+      <c r="F51" s="71"/>
+      <c r="G51" s="71"/>
+      <c r="H51" s="71"/>
     </row>
     <row r="52" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C52" s="79" t="s">
+      <c r="C52" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="D52" s="79"/>
-      <c r="E52" s="79"/>
-      <c r="F52" s="79"/>
-      <c r="G52" s="79"/>
-      <c r="H52" s="79"/>
+      <c r="D52" s="71"/>
+      <c r="E52" s="71"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="71"/>
+      <c r="H52" s="71"/>
     </row>
     <row r="53" spans="3:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="C53" s="79" t="s">
+      <c r="C53" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="D53" s="79"/>
-      <c r="E53" s="79"/>
-      <c r="F53" s="79"/>
-      <c r="G53" s="79"/>
-      <c r="H53" s="79"/>
+      <c r="D53" s="71"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="71"/>
+      <c r="H53" s="71"/>
     </row>
     <row r="54" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C54" s="79" t="s">
+      <c r="C54" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="D54" s="79"/>
-      <c r="E54" s="79"/>
-      <c r="F54" s="79"/>
-      <c r="G54" s="79"/>
-      <c r="H54" s="79"/>
+      <c r="D54" s="71"/>
+      <c r="E54" s="71"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="71"/>
     </row>
     <row r="55" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C55" s="79" t="s">
+      <c r="C55" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="D55" s="79"/>
-      <c r="E55" s="79"/>
-      <c r="F55" s="79"/>
-      <c r="G55" s="79"/>
-      <c r="H55" s="79"/>
+      <c r="D55" s="71"/>
+      <c r="E55" s="71"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="71"/>
+      <c r="H55" s="71"/>
     </row>
     <row r="56" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C56" s="79" t="s">
+      <c r="C56" s="71" t="s">
         <v>60</v>
       </c>
-      <c r="D56" s="79"/>
-      <c r="E56" s="79"/>
-      <c r="F56" s="79"/>
-      <c r="G56" s="79"/>
-      <c r="H56" s="79"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="71"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="71"/>
+      <c r="H56" s="71"/>
     </row>
     <row r="57" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C57" s="79" t="s">
+      <c r="C57" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="D57" s="79"/>
-      <c r="E57" s="79"/>
-      <c r="F57" s="79"/>
-      <c r="G57" s="79"/>
-      <c r="H57" s="79"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="71"/>
+      <c r="H57" s="71"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
